--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165938</v>
+        <v>128165947</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729946</v>
+        <v>730042</v>
       </c>
       <c r="R3" t="n">
-        <v>7121687</v>
+        <v>7121730</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -854,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165919</v>
+        <v>128165938</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,34 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729911</v>
+        <v>729946</v>
       </c>
       <c r="R4" t="n">
-        <v>7121731</v>
+        <v>7121687</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -946,17 +945,13 @@
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -975,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128165947</v>
+        <v>128165919</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730042</v>
+        <v>729911</v>
       </c>
       <c r="R5" t="n">
-        <v>7121730</v>
+        <v>7121731</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1046,6 +1041,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2062,45 +2062,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165946</v>
+        <v>128165922</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>91315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730160</v>
+        <v>730083</v>
       </c>
       <c r="R16" t="n">
-        <v>7121748</v>
+        <v>7121514</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2141,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2159,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165961</v>
+        <v>128165935</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>97345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2194,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729905</v>
+        <v>730109</v>
       </c>
       <c r="R17" t="n">
-        <v>7121772</v>
+        <v>7121506</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2256,48 +2260,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128165922</v>
+        <v>128165946</v>
       </c>
       <c r="B18" t="n">
-        <v>91315</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730083</v>
+        <v>730160</v>
       </c>
       <c r="R18" t="n">
-        <v>7121514</v>
+        <v>7121748</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2338,7 +2339,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2357,7 +2357,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128165962</v>
+        <v>128165961</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>729916</v>
+        <v>729905</v>
       </c>
       <c r="R19" t="n">
-        <v>7121715</v>
+        <v>7121772</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128165935</v>
+        <v>128165962</v>
       </c>
       <c r="B20" t="n">
-        <v>97345</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730109</v>
+        <v>729916</v>
       </c>
       <c r="R20" t="n">
-        <v>7121506</v>
+        <v>7121715</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2551,49 +2551,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128165940</v>
+        <v>128165960</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>729939</v>
+        <v>729928</v>
       </c>
       <c r="R21" t="n">
-        <v>7121786</v>
+        <v>7121753</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2653,7 +2652,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165960</v>
+        <v>128165956</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2682,19 +2681,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729928</v>
+        <v>729958</v>
       </c>
       <c r="R22" t="n">
-        <v>7121753</v>
+        <v>7121839</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2735,7 +2731,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2754,10 +2749,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128165956</v>
+        <v>128165930</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2765,34 +2760,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729958</v>
+        <v>730154</v>
       </c>
       <c r="R23" t="n">
-        <v>7121839</v>
+        <v>7121446</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2825,6 +2824,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2851,7 +2855,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165930</v>
+        <v>128165931</v>
       </c>
       <c r="B24" t="n">
         <v>57672</v>
@@ -2880,20 +2884,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730154</v>
+        <v>730017</v>
       </c>
       <c r="R24" t="n">
-        <v>7121446</v>
+        <v>7121813</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på samma tall</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2957,32 +2957,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128165931</v>
+        <v>128165974</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730017</v>
+        <v>729928</v>
       </c>
       <c r="R25" t="n">
-        <v>7121813</v>
+        <v>7121682</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3028,11 +3028,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3059,32 +3054,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128165974</v>
+        <v>128165959</v>
       </c>
       <c r="B26" t="n">
-        <v>98385</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3089,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729928</v>
+        <v>729945</v>
       </c>
       <c r="R26" t="n">
-        <v>7121682</v>
+        <v>7121797</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3156,7 +3151,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128165959</v>
+        <v>128165951</v>
       </c>
       <c r="B27" t="n">
         <v>79029</v>
@@ -3191,10 +3186,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729945</v>
+        <v>730024</v>
       </c>
       <c r="R27" t="n">
-        <v>7121797</v>
+        <v>7121785</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3253,10 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128165951</v>
+        <v>128165926</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3264,21 +3259,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3288,10 +3283,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730024</v>
+        <v>730131</v>
       </c>
       <c r="R28" t="n">
-        <v>7121785</v>
+        <v>7121481</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3350,10 +3345,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128165926</v>
+        <v>128165969</v>
       </c>
       <c r="B29" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3361,34 +3356,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730131</v>
+        <v>730111</v>
       </c>
       <c r="R29" t="n">
-        <v>7121481</v>
+        <v>7121506</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3429,6 +3427,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3447,10 +3446,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128165969</v>
+        <v>128165933</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,26 +3457,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730111</v>
+        <v>730045</v>
       </c>
       <c r="R30" t="n">
-        <v>7121506</v>
+        <v>7121802</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3523,13 +3523,17 @@
           <t>2025-09-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3548,7 +3552,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128165933</v>
+        <v>128165932</v>
       </c>
       <c r="B31" t="n">
         <v>57672</v>
@@ -3577,20 +3581,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730045</v>
+        <v>730083</v>
       </c>
       <c r="R31" t="n">
-        <v>7121802</v>
+        <v>7121500</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128165932</v>
+        <v>128165955</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730083</v>
+        <v>729973</v>
       </c>
       <c r="R32" t="n">
-        <v>7121500</v>
+        <v>7121813</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,11 +3725,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3756,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128165955</v>
+        <v>128165934</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3767,21 +3762,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3791,10 +3786,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>729973</v>
+        <v>730051</v>
       </c>
       <c r="R33" t="n">
-        <v>7121813</v>
+        <v>7121815</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3827,6 +3822,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3853,53 +3853,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128165941</v>
+        <v>128165957</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>729946</v>
+        <v>729953</v>
       </c>
       <c r="R34" t="n">
-        <v>7121788</v>
+        <v>7121824</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3940,7 +3932,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3959,10 +3950,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128165934</v>
+        <v>128165948</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3970,21 +3961,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3994,10 +3985,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730051</v>
+        <v>730039</v>
       </c>
       <c r="R35" t="n">
-        <v>7121815</v>
+        <v>7121748</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4030,11 +4021,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4061,7 +4047,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128165957</v>
+        <v>128165967</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4090,16 +4076,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729953</v>
+        <v>730095</v>
       </c>
       <c r="R36" t="n">
-        <v>7121824</v>
+        <v>7121521</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4140,6 +4129,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4158,7 +4148,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128165948</v>
+        <v>128165971</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4187,16 +4177,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730039</v>
+        <v>730158</v>
       </c>
       <c r="R37" t="n">
-        <v>7121748</v>
+        <v>7121446</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4237,6 +4230,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4255,32 +4249,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128165967</v>
+        <v>128165928</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4287,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730095</v>
+        <v>729932</v>
       </c>
       <c r="R38" t="n">
-        <v>7121521</v>
+        <v>7121695</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4356,10 +4350,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128165971</v>
+        <v>128165942</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4367,37 +4361,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730158</v>
+        <v>730136</v>
       </c>
       <c r="R39" t="n">
-        <v>7121446</v>
+        <v>7121772</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4438,7 +4429,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4457,48 +4447,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128165928</v>
+        <v>128165958</v>
       </c>
       <c r="B40" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729932</v>
+        <v>729942</v>
       </c>
       <c r="R40" t="n">
-        <v>7121695</v>
+        <v>7121803</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4539,7 +4526,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4558,10 +4544,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128165927</v>
+        <v>128165965</v>
       </c>
       <c r="B41" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,34 +4555,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730137</v>
+        <v>730086</v>
       </c>
       <c r="R41" t="n">
-        <v>7121478</v>
+        <v>7121516</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4637,6 +4626,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4655,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128165942</v>
+        <v>128165927</v>
       </c>
       <c r="B42" t="n">
-        <v>91368</v>
+        <v>91350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4666,21 +4656,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4690,10 +4680,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730136</v>
+        <v>730137</v>
       </c>
       <c r="R42" t="n">
-        <v>7121772</v>
+        <v>7121478</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4752,45 +4742,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128165958</v>
+        <v>128165939</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729942</v>
+        <v>729923</v>
       </c>
       <c r="R43" t="n">
-        <v>7121803</v>
+        <v>7121820</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4831,6 +4825,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4849,10 +4844,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128165965</v>
+        <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>91646</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,40 +4855,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730086</v>
+        <v>730055</v>
       </c>
       <c r="R44" t="n">
-        <v>7121516</v>
+        <v>7121821</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4931,71 +4923,66 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128165939</v>
+        <v>128221493</v>
       </c>
       <c r="B45" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>729923</v>
+        <v>730032</v>
       </c>
       <c r="R45" t="n">
-        <v>7121820</v>
+        <v>7121700</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5027,28 +5014,2105 @@
           <t>2025-09-01</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128221497</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>730112</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7121785</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128221496</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>730168</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7121738</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128221503</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>730239</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7121592</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128221495</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>730262</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7121551</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128221481</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91315</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>730240</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7121639</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128221484</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>730055</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7121821</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128221483</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91315</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>730169</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7121486</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128165940</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>729939</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7121786</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
           <t>Alva Danielsson</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
+      <c r="AX53" t="inlineStr">
         <is>
           <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128221487</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80161</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>730102</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7121795</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128221482</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91315</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>730021</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7121603</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128221489</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>730051</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7121646</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128165941</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>729946</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7121788</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128221500</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>730091</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7121561</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128221486</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>730186</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7121516</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128221494</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>730250</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7121538</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128221485</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>730021</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7121603</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128221498</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>730083</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7121587</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128221502</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>730247</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7121509</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128221480</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91315</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>730261</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7121621</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128221479</v>
+      </c>
+      <c r="B65" t="n">
+        <v>96720</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>730141</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7121775</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128221499</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>730110</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7121785</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165963</v>
+        <v>128165938</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730066</v>
+        <v>729946</v>
       </c>
       <c r="R2" t="n">
-        <v>7121525</v>
+        <v>7121687</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165947</v>
+        <v>128165963</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730042</v>
+        <v>730066</v>
       </c>
       <c r="R3" t="n">
-        <v>7121730</v>
+        <v>7121525</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165938</v>
+        <v>128165947</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +884,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729946</v>
+        <v>730042</v>
       </c>
       <c r="R4" t="n">
-        <v>7121687</v>
+        <v>7121730</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -951,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128165949</v>
+        <v>128165970</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1295,16 +1295,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730055</v>
+        <v>730103</v>
       </c>
       <c r="R8" t="n">
-        <v>7121817</v>
+        <v>7121499</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1345,6 +1348,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1363,7 +1367,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128165970</v>
+        <v>128165949</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1392,19 +1396,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730103</v>
+        <v>730055</v>
       </c>
       <c r="R9" t="n">
-        <v>7121499</v>
+        <v>7121817</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1445,7 +1446,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128165925</v>
+        <v>128165943</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730049</v>
+        <v>730059</v>
       </c>
       <c r="R13" t="n">
-        <v>7121812</v>
+        <v>7121540</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128165943</v>
+        <v>128165925</v>
       </c>
       <c r="B14" t="n">
-        <v>91368</v>
+        <v>91351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730059</v>
+        <v>730049</v>
       </c>
       <c r="R14" t="n">
-        <v>7121540</v>
+        <v>7121812</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1964,7 +1964,7 @@
         <v>128165944</v>
       </c>
       <c r="B15" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,48 +2062,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165922</v>
+        <v>128165946</v>
       </c>
       <c r="B16" t="n">
-        <v>91315</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730083</v>
+        <v>730160</v>
       </c>
       <c r="R16" t="n">
-        <v>7121514</v>
+        <v>7121748</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2144,7 +2141,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,32 +2159,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165935</v>
+        <v>128165961</v>
       </c>
       <c r="B17" t="n">
-        <v>97345</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2194,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730109</v>
+        <v>729905</v>
       </c>
       <c r="R17" t="n">
-        <v>7121506</v>
+        <v>7121772</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2260,45 +2256,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128165946</v>
+        <v>128165922</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>91316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730160</v>
+        <v>730083</v>
       </c>
       <c r="R18" t="n">
-        <v>7121748</v>
+        <v>7121514</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2339,6 +2338,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2357,7 +2357,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128165961</v>
+        <v>128165962</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>729905</v>
+        <v>729916</v>
       </c>
       <c r="R19" t="n">
-        <v>7121772</v>
+        <v>7121715</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128165962</v>
+        <v>128165935</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>97346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>729916</v>
+        <v>730109</v>
       </c>
       <c r="R20" t="n">
-        <v>7121715</v>
+        <v>7121506</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165956</v>
+        <v>128165930</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,34 +2663,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729958</v>
+        <v>730154</v>
       </c>
       <c r="R22" t="n">
-        <v>7121839</v>
+        <v>7121446</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2723,6 +2727,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2749,7 +2758,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128165930</v>
+        <v>128165931</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2778,20 +2787,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730154</v>
+        <v>730017</v>
       </c>
       <c r="R23" t="n">
-        <v>7121446</v>
+        <v>7121813</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2828,7 +2833,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på samma tall</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2855,10 +2860,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165931</v>
+        <v>128165956</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2866,21 +2871,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2890,10 +2895,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730017</v>
+        <v>729958</v>
       </c>
       <c r="R24" t="n">
-        <v>7121813</v>
+        <v>7121839</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2926,11 +2931,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2960,7 +2960,7 @@
         <v>128165974</v>
       </c>
       <c r="B25" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>128165926</v>
       </c>
       <c r="B28" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128165942</v>
+        <v>128165927</v>
       </c>
       <c r="B39" t="n">
-        <v>91368</v>
+        <v>91351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4361,21 +4361,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730136</v>
+        <v>730137</v>
       </c>
       <c r="R39" t="n">
-        <v>7121772</v>
+        <v>7121478</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4645,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128165927</v>
+        <v>128165942</v>
       </c>
       <c r="B42" t="n">
-        <v>91350</v>
+        <v>91369</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4656,21 +4656,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730137</v>
+        <v>730136</v>
       </c>
       <c r="R42" t="n">
-        <v>7121478</v>
+        <v>7121772</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4745,7 +4745,7 @@
         <v>128165939</v>
       </c>
       <c r="B43" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5238,10 +5238,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128221503</v>
+        <v>128221495</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5249,21 +5249,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730239</v>
+        <v>730262</v>
       </c>
       <c r="R48" t="n">
-        <v>7121592</v>
+        <v>7121551</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5309,11 +5309,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5340,10 +5335,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128221495</v>
+        <v>128221503</v>
       </c>
       <c r="B49" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5351,21 +5346,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5375,10 +5370,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730262</v>
+        <v>730239</v>
       </c>
       <c r="R49" t="n">
-        <v>7121551</v>
+        <v>7121592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5411,6 +5406,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5631,48 +5631,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B52" t="n">
-        <v>91315</v>
+        <v>98469</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R52" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5710,74 +5718,67 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B53" t="n">
-        <v>98468</v>
+        <v>91316</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R53" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5815,19 +5816,18 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5934,7 +5934,7 @@
         <v>128221482</v>
       </c>
       <c r="B55" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>128165941</v>
       </c>
       <c r="B57" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221500</v>
       </c>
       <c r="B58" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128221486</v>
       </c>
       <c r="B59" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6631,32 +6631,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128221498</v>
+        <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>98468</v>
+        <v>91369</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730083</v>
+        <v>730247</v>
       </c>
       <c r="R62" t="n">
-        <v>7121587</v>
+        <v>7121509</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6728,32 +6728,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128221502</v>
+        <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91368</v>
+        <v>91316</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730247</v>
+        <v>730261</v>
       </c>
       <c r="R63" t="n">
-        <v>7121509</v>
+        <v>7121621</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6825,32 +6825,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128221480</v>
+        <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>91315</v>
+        <v>98469</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>730261</v>
+        <v>730083</v>
       </c>
       <c r="R64" t="n">
-        <v>7121621</v>
+        <v>7121587</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165938</v>
+        <v>128165919</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729946</v>
+        <v>729911</v>
       </c>
       <c r="R2" t="n">
-        <v>7121687</v>
+        <v>7121731</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,13 +748,17 @@
           <t>2025-09-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -970,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128165919</v>
+        <v>128165938</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,34 +982,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729911</v>
+        <v>729946</v>
       </c>
       <c r="R5" t="n">
-        <v>7121731</v>
+        <v>7121687</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1043,17 +1047,13 @@
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128165949</v>
+        <v>128165950</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730055</v>
+        <v>730039</v>
       </c>
       <c r="R9" t="n">
-        <v>7121817</v>
+        <v>7121797</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128165950</v>
+        <v>128165972</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1493,16 +1493,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730039</v>
+        <v>730154</v>
       </c>
       <c r="R10" t="n">
-        <v>7121797</v>
+        <v>7121458</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1543,6 +1546,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1561,7 +1565,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128165972</v>
+        <v>128165949</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1590,19 +1594,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730154</v>
+        <v>730055</v>
       </c>
       <c r="R11" t="n">
-        <v>7121458</v>
+        <v>7121817</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1643,7 +1644,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>128165943</v>
       </c>
       <c r="B13" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128165925</v>
       </c>
       <c r="B14" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>128165944</v>
       </c>
       <c r="B15" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,45 +2062,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165946</v>
+        <v>128165922</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>91317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730160</v>
+        <v>730083</v>
       </c>
       <c r="R16" t="n">
-        <v>7121748</v>
+        <v>7121514</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2141,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2159,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165961</v>
+        <v>128165935</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>97347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2194,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729905</v>
+        <v>730109</v>
       </c>
       <c r="R17" t="n">
-        <v>7121772</v>
+        <v>7121506</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2256,48 +2260,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128165922</v>
+        <v>128165962</v>
       </c>
       <c r="B18" t="n">
-        <v>91316</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730083</v>
+        <v>729916</v>
       </c>
       <c r="R18" t="n">
-        <v>7121514</v>
+        <v>7121715</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2338,7 +2339,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2357,7 +2357,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128165962</v>
+        <v>128165946</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>729916</v>
+        <v>730160</v>
       </c>
       <c r="R19" t="n">
-        <v>7121715</v>
+        <v>7121748</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128165935</v>
+        <v>128165961</v>
       </c>
       <c r="B20" t="n">
-        <v>97346</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730109</v>
+        <v>729905</v>
       </c>
       <c r="R20" t="n">
-        <v>7121506</v>
+        <v>7121772</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2960,7 +2960,7 @@
         <v>128165974</v>
       </c>
       <c r="B25" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128165926</v>
+        <v>128165969</v>
       </c>
       <c r="B28" t="n">
-        <v>91351</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3259,34 +3259,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730131</v>
+        <v>730111</v>
       </c>
       <c r="R28" t="n">
-        <v>7121481</v>
+        <v>7121506</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3327,6 +3330,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3345,10 +3349,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128165969</v>
+        <v>128165926</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3356,37 +3360,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730111</v>
+        <v>730131</v>
       </c>
       <c r="R29" t="n">
-        <v>7121506</v>
+        <v>7121481</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3427,7 +3428,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128165933</v>
+        <v>128165955</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3457,38 +3457,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730045</v>
+        <v>729973</v>
       </c>
       <c r="R30" t="n">
-        <v>7121802</v>
+        <v>7121813</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3521,11 +3517,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3552,7 +3543,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128165932</v>
+        <v>128165933</v>
       </c>
       <c r="B31" t="n">
         <v>57672</v>
@@ -3581,16 +3572,20 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730083</v>
+        <v>730045</v>
       </c>
       <c r="R31" t="n">
-        <v>7121500</v>
+        <v>7121802</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3649,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128165955</v>
+        <v>128165932</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,21 +3660,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,10 +3684,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>729973</v>
+        <v>730083</v>
       </c>
       <c r="R32" t="n">
-        <v>7121813</v>
+        <v>7121500</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,6 +3720,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3853,7 +3853,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128165957</v>
+        <v>128165948</v>
       </c>
       <c r="B34" t="n">
         <v>79029</v>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>729953</v>
+        <v>730039</v>
       </c>
       <c r="R34" t="n">
-        <v>7121824</v>
+        <v>7121748</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3950,7 +3950,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128165948</v>
+        <v>128165957</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730039</v>
+        <v>729953</v>
       </c>
       <c r="R35" t="n">
-        <v>7121748</v>
+        <v>7121824</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128165967</v>
+        <v>128165971</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730095</v>
+        <v>730158</v>
       </c>
       <c r="R36" t="n">
-        <v>7121521</v>
+        <v>7121446</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128165971</v>
+        <v>128165967</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730158</v>
+        <v>730095</v>
       </c>
       <c r="R37" t="n">
-        <v>7121446</v>
+        <v>7121521</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128165927</v>
+        <v>128165958</v>
       </c>
       <c r="B39" t="n">
-        <v>91351</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4361,21 +4361,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730137</v>
+        <v>729942</v>
       </c>
       <c r="R39" t="n">
-        <v>7121478</v>
+        <v>7121803</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4447,7 +4447,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128165958</v>
+        <v>128165965</v>
       </c>
       <c r="B40" t="n">
         <v>79029</v>
@@ -4476,16 +4476,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729942</v>
+        <v>730086</v>
       </c>
       <c r="R40" t="n">
-        <v>7121803</v>
+        <v>7121516</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4526,6 +4529,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4544,10 +4548,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128165965</v>
+        <v>128165942</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4555,37 +4559,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730086</v>
+        <v>730136</v>
       </c>
       <c r="R41" t="n">
-        <v>7121516</v>
+        <v>7121772</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4626,7 +4627,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4645,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128165942</v>
+        <v>128165927</v>
       </c>
       <c r="B42" t="n">
-        <v>91369</v>
+        <v>91352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4656,21 +4656,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730136</v>
+        <v>730137</v>
       </c>
       <c r="R42" t="n">
-        <v>7121772</v>
+        <v>7121478</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4745,7 +4745,7 @@
         <v>128165939</v>
       </c>
       <c r="B43" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5631,56 +5631,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>98469</v>
+        <v>91317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R52" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5718,67 +5710,74 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B53" t="n">
-        <v>91316</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R53" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5816,28 +5815,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128221487</v>
+        <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>80161</v>
+        <v>91317</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,34 +5845,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730102</v>
+        <v>730021</v>
       </c>
       <c r="R54" t="n">
-        <v>7121795</v>
+        <v>7121603</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5913,6 +5916,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5931,10 +5935,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128221482</v>
+        <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>91316</v>
+        <v>80161</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,37 +5946,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730021</v>
+        <v>730102</v>
       </c>
       <c r="R55" t="n">
-        <v>7121603</v>
+        <v>7121795</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6013,7 +6014,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>128165941</v>
       </c>
       <c r="B57" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6235,45 +6235,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221500</v>
+        <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>98469</v>
+        <v>91352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730091</v>
+        <v>730186</v>
       </c>
       <c r="R58" t="n">
-        <v>7121561</v>
+        <v>7121516</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6314,6 +6317,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6332,48 +6336,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221486</v>
+        <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>91351</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730186</v>
+        <v>730091</v>
       </c>
       <c r="R59" t="n">
-        <v>7121516</v>
+        <v>7121561</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6414,7 +6415,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128221494</v>
+        <v>128221485</v>
       </c>
       <c r="B60" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,34 +6444,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730250</v>
+        <v>730021</v>
       </c>
       <c r="R60" t="n">
-        <v>7121538</v>
+        <v>7121603</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6512,6 +6515,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6530,10 +6534,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128221485</v>
+        <v>128221494</v>
       </c>
       <c r="B61" t="n">
-        <v>91351</v>
+        <v>80132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6541,37 +6545,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730021</v>
+        <v>730250</v>
       </c>
       <c r="R61" t="n">
-        <v>7121603</v>
+        <v>7121538</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6612,7 +6613,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165919</v>
+        <v>128165963</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729911</v>
+        <v>730066</v>
       </c>
       <c r="R2" t="n">
-        <v>7121731</v>
+        <v>7121525</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165963</v>
+        <v>128165947</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730066</v>
+        <v>730042</v>
       </c>
       <c r="R3" t="n">
-        <v>7121525</v>
+        <v>7121730</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165947</v>
+        <v>128165938</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730042</v>
+        <v>729946</v>
       </c>
       <c r="R4" t="n">
-        <v>7121730</v>
+        <v>7121687</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -953,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -971,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128165938</v>
+        <v>128165919</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,37 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729946</v>
+        <v>729911</v>
       </c>
       <c r="R5" t="n">
-        <v>7121687</v>
+        <v>7121731</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1047,13 +1043,17 @@
           <t>2025-09-01</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128165970</v>
+        <v>128165949</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1295,19 +1295,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730103</v>
+        <v>730055</v>
       </c>
       <c r="R8" t="n">
-        <v>7121499</v>
+        <v>7121817</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1348,7 +1345,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1565,7 +1561,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128165949</v>
+        <v>128165970</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1594,16 +1590,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730055</v>
+        <v>730103</v>
       </c>
       <c r="R11" t="n">
-        <v>7121817</v>
+        <v>7121499</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1644,6 +1643,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128165943</v>
+        <v>128165925</v>
       </c>
       <c r="B13" t="n">
-        <v>91370</v>
+        <v>91352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730059</v>
+        <v>730049</v>
       </c>
       <c r="R13" t="n">
-        <v>7121540</v>
+        <v>7121812</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128165925</v>
+        <v>128165943</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>91370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730049</v>
+        <v>730059</v>
       </c>
       <c r="R14" t="n">
-        <v>7121812</v>
+        <v>7121540</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128165959</v>
+        <v>128165951</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729945</v>
+        <v>730024</v>
       </c>
       <c r="R26" t="n">
-        <v>7121797</v>
+        <v>7121785</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128165951</v>
+        <v>128165959</v>
       </c>
       <c r="B27" t="n">
         <v>79029</v>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730024</v>
+        <v>729945</v>
       </c>
       <c r="R27" t="n">
-        <v>7121785</v>
+        <v>7121797</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128165969</v>
+        <v>128165926</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3259,37 +3259,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730111</v>
+        <v>730131</v>
       </c>
       <c r="R28" t="n">
-        <v>7121506</v>
+        <v>7121481</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3330,7 +3327,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3349,10 +3345,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128165926</v>
+        <v>128165969</v>
       </c>
       <c r="B29" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3360,34 +3356,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730131</v>
+        <v>730111</v>
       </c>
       <c r="R29" t="n">
-        <v>7121481</v>
+        <v>7121506</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3428,6 +3427,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128165948</v>
+        <v>128165957</v>
       </c>
       <c r="B34" t="n">
         <v>79029</v>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730039</v>
+        <v>729953</v>
       </c>
       <c r="R34" t="n">
-        <v>7121748</v>
+        <v>7121824</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3950,7 +3950,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128165957</v>
+        <v>128165948</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729953</v>
+        <v>730039</v>
       </c>
       <c r="R35" t="n">
-        <v>7121824</v>
+        <v>7121748</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128165971</v>
+        <v>128165967</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730158</v>
+        <v>730095</v>
       </c>
       <c r="R36" t="n">
-        <v>7121446</v>
+        <v>7121521</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128165967</v>
+        <v>128165971</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730095</v>
+        <v>730158</v>
       </c>
       <c r="R37" t="n">
-        <v>7121521</v>
+        <v>7121446</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128165958</v>
+        <v>128165965</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4379,16 +4379,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729942</v>
+        <v>730086</v>
       </c>
       <c r="R39" t="n">
-        <v>7121803</v>
+        <v>7121516</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4429,6 +4432,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4447,7 +4451,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128165965</v>
+        <v>128165958</v>
       </c>
       <c r="B40" t="n">
         <v>79029</v>
@@ -4476,19 +4480,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730086</v>
+        <v>729942</v>
       </c>
       <c r="R40" t="n">
-        <v>7121516</v>
+        <v>7121803</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4529,7 +4530,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4548,10 +4548,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128165942</v>
+        <v>128165927</v>
       </c>
       <c r="B41" t="n">
-        <v>91370</v>
+        <v>91352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4559,21 +4559,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730136</v>
+        <v>730137</v>
       </c>
       <c r="R41" t="n">
-        <v>7121772</v>
+        <v>7121478</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4645,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128165927</v>
+        <v>128165942</v>
       </c>
       <c r="B42" t="n">
-        <v>91352</v>
+        <v>91370</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4656,21 +4656,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730137</v>
+        <v>730136</v>
       </c>
       <c r="R42" t="n">
-        <v>7121478</v>
+        <v>7121772</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5043,7 +5043,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128221497</v>
+        <v>128221496</v>
       </c>
       <c r="B46" t="n">
         <v>98470</v>
@@ -5078,10 +5078,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730112</v>
+        <v>730168</v>
       </c>
       <c r="R46" t="n">
-        <v>7121785</v>
+        <v>7121738</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5122,6 +5122,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5140,7 +5141,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128221496</v>
+        <v>128221497</v>
       </c>
       <c r="B47" t="n">
         <v>98470</v>
@@ -5175,10 +5176,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730168</v>
+        <v>730112</v>
       </c>
       <c r="R47" t="n">
-        <v>7121738</v>
+        <v>7121785</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5219,7 +5220,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6032,48 +6032,56 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128221489</v>
+        <v>128165941</v>
       </c>
       <c r="B56" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730051</v>
+        <v>729946</v>
       </c>
       <c r="R56" t="n">
-        <v>7121646</v>
+        <v>7121788</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6111,74 +6119,67 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128165941</v>
+        <v>128221489</v>
       </c>
       <c r="B57" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729946</v>
+        <v>730051</v>
       </c>
       <c r="R57" t="n">
-        <v>7121788</v>
+        <v>7121646</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6216,19 +6217,18 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6631,32 +6631,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128221502</v>
+        <v>128221480</v>
       </c>
       <c r="B62" t="n">
-        <v>91370</v>
+        <v>91317</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730247</v>
+        <v>730261</v>
       </c>
       <c r="R62" t="n">
-        <v>7121509</v>
+        <v>7121621</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6728,32 +6728,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128221480</v>
+        <v>128221502</v>
       </c>
       <c r="B63" t="n">
-        <v>91317</v>
+        <v>91370</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730261</v>
+        <v>730247</v>
       </c>
       <c r="R63" t="n">
-        <v>7121621</v>
+        <v>7121509</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -1266,7 +1266,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128165949</v>
+        <v>128165970</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1295,16 +1295,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730055</v>
+        <v>730103</v>
       </c>
       <c r="R8" t="n">
-        <v>7121817</v>
+        <v>7121499</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1345,6 +1348,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1363,7 +1367,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128165950</v>
+        <v>128165949</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1398,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730039</v>
+        <v>730055</v>
       </c>
       <c r="R9" t="n">
-        <v>7121797</v>
+        <v>7121817</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,7 +1464,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128165972</v>
+        <v>128165950</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1489,19 +1493,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730154</v>
+        <v>730039</v>
       </c>
       <c r="R10" t="n">
-        <v>7121458</v>
+        <v>7121797</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1542,7 +1543,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128165970</v>
+        <v>128165972</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730103</v>
+        <v>730154</v>
       </c>
       <c r="R11" t="n">
-        <v>7121499</v>
+        <v>7121458</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165930</v>
+        <v>128165956</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,38 +2663,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730154</v>
+        <v>729958</v>
       </c>
       <c r="R22" t="n">
-        <v>7121446</v>
+        <v>7121839</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2727,11 +2723,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2758,7 +2749,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128165931</v>
+        <v>128165930</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2787,16 +2778,20 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730017</v>
+        <v>730154</v>
       </c>
       <c r="R23" t="n">
-        <v>7121813</v>
+        <v>7121446</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2833,7 +2828,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2860,10 +2855,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165956</v>
+        <v>128165931</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2871,21 +2866,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2895,10 +2890,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729958</v>
+        <v>730017</v>
       </c>
       <c r="R24" t="n">
-        <v>7121839</v>
+        <v>7121813</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2931,6 +2926,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5631,48 +5631,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B52" t="n">
-        <v>91317</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R52" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5710,74 +5718,67 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>91317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R53" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5815,19 +5816,18 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6235,48 +6235,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221486</v>
+        <v>128221500</v>
       </c>
       <c r="B58" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730186</v>
+        <v>730091</v>
       </c>
       <c r="R58" t="n">
-        <v>7121516</v>
+        <v>7121561</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6317,7 +6314,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6336,45 +6332,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221500</v>
+        <v>128221486</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730091</v>
+        <v>730186</v>
       </c>
       <c r="R59" t="n">
-        <v>7121561</v>
+        <v>7121516</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6415,6 +6414,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165963</v>
+        <v>128165938</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730066</v>
+        <v>729946</v>
       </c>
       <c r="R2" t="n">
-        <v>7121525</v>
+        <v>7121687</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165947</v>
+        <v>128165963</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730042</v>
+        <v>730066</v>
       </c>
       <c r="R3" t="n">
-        <v>7121730</v>
+        <v>7121525</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165938</v>
+        <v>128165947</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +884,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729946</v>
+        <v>730042</v>
       </c>
       <c r="R4" t="n">
-        <v>7121687</v>
+        <v>7121730</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -951,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128165970</v>
+        <v>128165949</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1295,19 +1295,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730103</v>
+        <v>730055</v>
       </c>
       <c r="R8" t="n">
-        <v>7121499</v>
+        <v>7121817</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1348,7 +1345,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1367,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128165949</v>
+        <v>128165950</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1402,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730055</v>
+        <v>730039</v>
       </c>
       <c r="R9" t="n">
-        <v>7121817</v>
+        <v>7121797</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1464,7 +1460,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128165950</v>
+        <v>128165972</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1493,16 +1489,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730039</v>
+        <v>730154</v>
       </c>
       <c r="R10" t="n">
-        <v>7121797</v>
+        <v>7121458</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1543,6 +1542,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128165972</v>
+        <v>128165970</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730154</v>
+        <v>730103</v>
       </c>
       <c r="R11" t="n">
-        <v>7121458</v>
+        <v>7121499</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165922</v>
+        <v>128165935</v>
       </c>
       <c r="B16" t="n">
-        <v>91317</v>
+        <v>97347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2073,37 +2073,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730083</v>
+        <v>730109</v>
       </c>
       <c r="R16" t="n">
-        <v>7121514</v>
+        <v>7121506</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2144,7 +2141,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,10 +2159,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165935</v>
+        <v>128165922</v>
       </c>
       <c r="B17" t="n">
-        <v>97347</v>
+        <v>91317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,34 +2170,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730109</v>
+        <v>730083</v>
       </c>
       <c r="R17" t="n">
-        <v>7121506</v>
+        <v>7121514</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2242,6 +2241,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165956</v>
+        <v>128165930</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,34 +2663,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729958</v>
+        <v>730154</v>
       </c>
       <c r="R22" t="n">
-        <v>7121839</v>
+        <v>7121446</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2723,6 +2727,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2749,7 +2758,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128165930</v>
+        <v>128165931</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2778,20 +2787,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730154</v>
+        <v>730017</v>
       </c>
       <c r="R23" t="n">
-        <v>7121446</v>
+        <v>7121813</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2828,7 +2833,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på samma tall</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2855,10 +2860,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165931</v>
+        <v>128165956</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2866,21 +2871,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2890,10 +2895,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730017</v>
+        <v>729958</v>
       </c>
       <c r="R24" t="n">
-        <v>7121813</v>
+        <v>7121839</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2926,11 +2931,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3248,10 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128165926</v>
+        <v>128165969</v>
       </c>
       <c r="B28" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3259,34 +3259,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730131</v>
+        <v>730111</v>
       </c>
       <c r="R28" t="n">
-        <v>7121481</v>
+        <v>7121506</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3327,6 +3330,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3345,10 +3349,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128165969</v>
+        <v>128165926</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3356,37 +3360,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730111</v>
+        <v>730131</v>
       </c>
       <c r="R29" t="n">
-        <v>7121506</v>
+        <v>7121481</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3427,7 +3428,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -5631,56 +5631,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>91317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R52" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5718,67 +5710,74 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B53" t="n">
-        <v>91317</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R53" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5816,18 +5815,19 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6235,45 +6235,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221500</v>
+        <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730091</v>
+        <v>730186</v>
       </c>
       <c r="R58" t="n">
-        <v>7121561</v>
+        <v>7121516</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6314,6 +6317,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6332,48 +6336,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221486</v>
+        <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730186</v>
+        <v>730091</v>
       </c>
       <c r="R59" t="n">
-        <v>7121516</v>
+        <v>7121561</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6414,7 +6415,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128221485</v>
+        <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>91352</v>
+        <v>80132</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,37 +6444,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730021</v>
+        <v>730250</v>
       </c>
       <c r="R60" t="n">
-        <v>7121603</v>
+        <v>7121538</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6515,7 +6512,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6534,10 +6530,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128221494</v>
+        <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6545,34 +6541,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730250</v>
+        <v>730021</v>
       </c>
       <c r="R61" t="n">
-        <v>7121538</v>
+        <v>7121603</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6613,6 +6612,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165938</v>
+        <v>128165963</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729946</v>
+        <v>730066</v>
       </c>
       <c r="R2" t="n">
-        <v>7121687</v>
+        <v>7121525</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165963</v>
+        <v>128165947</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -811,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730066</v>
+        <v>730042</v>
       </c>
       <c r="R3" t="n">
-        <v>7121525</v>
+        <v>7121730</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165947</v>
+        <v>128165938</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,34 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730042</v>
+        <v>729946</v>
       </c>
       <c r="R4" t="n">
-        <v>7121730</v>
+        <v>7121687</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -952,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165935</v>
+        <v>128165922</v>
       </c>
       <c r="B16" t="n">
-        <v>97347</v>
+        <v>91317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2073,34 +2073,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730109</v>
+        <v>730083</v>
       </c>
       <c r="R16" t="n">
-        <v>7121506</v>
+        <v>7121514</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2141,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2159,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165922</v>
+        <v>128165935</v>
       </c>
       <c r="B17" t="n">
-        <v>91317</v>
+        <v>97347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2170,37 +2174,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730083</v>
+        <v>730109</v>
       </c>
       <c r="R17" t="n">
-        <v>7121514</v>
+        <v>7121506</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2241,7 +2242,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128221481</v>
+        <v>128221484</v>
       </c>
       <c r="B50" t="n">
-        <v>91317</v>
+        <v>91352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730240</v>
+        <v>730055</v>
       </c>
       <c r="R50" t="n">
-        <v>7121639</v>
+        <v>7121821</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5534,32 +5534,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128221484</v>
+        <v>128221481</v>
       </c>
       <c r="B51" t="n">
-        <v>91352</v>
+        <v>91317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730055</v>
+        <v>730240</v>
       </c>
       <c r="R51" t="n">
-        <v>7121821</v>
+        <v>7121639</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5631,48 +5631,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B52" t="n">
-        <v>91317</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R52" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5710,74 +5718,67 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>91317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R53" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5815,19 +5816,18 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6235,48 +6235,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221486</v>
+        <v>128221500</v>
       </c>
       <c r="B58" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730186</v>
+        <v>730091</v>
       </c>
       <c r="R58" t="n">
-        <v>7121516</v>
+        <v>7121561</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6317,7 +6314,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6336,45 +6332,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221500</v>
+        <v>128221486</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730091</v>
+        <v>730186</v>
       </c>
       <c r="R59" t="n">
-        <v>7121561</v>
+        <v>7121516</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6415,6 +6414,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128221494</v>
+        <v>128221485</v>
       </c>
       <c r="B60" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,34 +6444,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730250</v>
+        <v>730021</v>
       </c>
       <c r="R60" t="n">
-        <v>7121538</v>
+        <v>7121603</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6512,6 +6515,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6530,10 +6534,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128221485</v>
+        <v>128221494</v>
       </c>
       <c r="B61" t="n">
-        <v>91352</v>
+        <v>80132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6541,37 +6545,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730021</v>
+        <v>730250</v>
       </c>
       <c r="R61" t="n">
-        <v>7121603</v>
+        <v>7121538</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6612,7 +6613,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -5437,32 +5437,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128221484</v>
+        <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91352</v>
+        <v>91317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730055</v>
+        <v>730240</v>
       </c>
       <c r="R50" t="n">
-        <v>7121821</v>
+        <v>7121639</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5534,32 +5534,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128221481</v>
+        <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91317</v>
+        <v>91352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730240</v>
+        <v>730055</v>
       </c>
       <c r="R51" t="n">
-        <v>7121639</v>
+        <v>7121821</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6235,45 +6235,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221500</v>
+        <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730091</v>
+        <v>730186</v>
       </c>
       <c r="R58" t="n">
-        <v>7121561</v>
+        <v>7121516</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6314,6 +6317,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6332,48 +6336,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221486</v>
+        <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730186</v>
+        <v>730091</v>
       </c>
       <c r="R59" t="n">
-        <v>7121516</v>
+        <v>7121561</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6414,7 +6415,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165963</v>
+        <v>128165938</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730066</v>
+        <v>729946</v>
       </c>
       <c r="R2" t="n">
-        <v>7121525</v>
+        <v>7121687</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165947</v>
+        <v>128165963</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730042</v>
+        <v>730066</v>
       </c>
       <c r="R3" t="n">
-        <v>7121730</v>
+        <v>7121525</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165938</v>
+        <v>128165947</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +884,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729946</v>
+        <v>730042</v>
       </c>
       <c r="R4" t="n">
-        <v>7121687</v>
+        <v>7121730</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -951,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165922</v>
+        <v>128165935</v>
       </c>
       <c r="B16" t="n">
-        <v>91317</v>
+        <v>97347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2073,37 +2073,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730083</v>
+        <v>730109</v>
       </c>
       <c r="R16" t="n">
-        <v>7121514</v>
+        <v>7121506</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2144,7 +2141,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,10 +2159,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165935</v>
+        <v>128165922</v>
       </c>
       <c r="B17" t="n">
-        <v>97347</v>
+        <v>91317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,34 +2170,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730109</v>
+        <v>730083</v>
       </c>
       <c r="R17" t="n">
-        <v>7121506</v>
+        <v>7121514</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2242,6 +2241,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165930</v>
+        <v>128165956</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,38 +2663,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730154</v>
+        <v>729958</v>
       </c>
       <c r="R22" t="n">
-        <v>7121446</v>
+        <v>7121839</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2727,11 +2723,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2758,7 +2749,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128165931</v>
+        <v>128165930</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2787,16 +2778,20 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730017</v>
+        <v>730154</v>
       </c>
       <c r="R23" t="n">
-        <v>7121813</v>
+        <v>7121446</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2833,7 +2828,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2860,10 +2855,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165956</v>
+        <v>128165931</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2871,21 +2866,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2895,10 +2890,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729958</v>
+        <v>730017</v>
       </c>
       <c r="R24" t="n">
-        <v>7121839</v>
+        <v>7121813</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2931,6 +2926,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3248,10 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128165969</v>
+        <v>128165926</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3259,37 +3259,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730111</v>
+        <v>730131</v>
       </c>
       <c r="R28" t="n">
-        <v>7121506</v>
+        <v>7121481</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3330,7 +3327,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3349,10 +3345,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128165926</v>
+        <v>128165969</v>
       </c>
       <c r="B29" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3360,34 +3356,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730131</v>
+        <v>730111</v>
       </c>
       <c r="R29" t="n">
-        <v>7121481</v>
+        <v>7121506</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3428,6 +3427,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128221481</v>
+        <v>128221484</v>
       </c>
       <c r="B50" t="n">
-        <v>91317</v>
+        <v>91352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730240</v>
+        <v>730055</v>
       </c>
       <c r="R50" t="n">
-        <v>7121639</v>
+        <v>7121821</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5534,32 +5534,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128221484</v>
+        <v>128221481</v>
       </c>
       <c r="B51" t="n">
-        <v>91352</v>
+        <v>91317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730055</v>
+        <v>730240</v>
       </c>
       <c r="R51" t="n">
-        <v>7121821</v>
+        <v>7121639</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5631,56 +5631,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>91317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R52" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5718,67 +5710,74 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B53" t="n">
-        <v>91317</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R53" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5816,18 +5815,19 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128221485</v>
+        <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>91352</v>
+        <v>80132</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,37 +6444,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730021</v>
+        <v>730250</v>
       </c>
       <c r="R60" t="n">
-        <v>7121603</v>
+        <v>7121538</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6515,7 +6512,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6534,10 +6530,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128221494</v>
+        <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6545,34 +6541,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730250</v>
+        <v>730021</v>
       </c>
       <c r="R61" t="n">
-        <v>7121538</v>
+        <v>7121603</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6613,6 +6612,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165938</v>
+        <v>128165963</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729946</v>
+        <v>730066</v>
       </c>
       <c r="R2" t="n">
-        <v>7121687</v>
+        <v>7121525</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165963</v>
+        <v>128165947</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -811,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730066</v>
+        <v>730042</v>
       </c>
       <c r="R3" t="n">
-        <v>7121525</v>
+        <v>7121730</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165947</v>
+        <v>128165938</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,34 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730042</v>
+        <v>729946</v>
       </c>
       <c r="R4" t="n">
-        <v>7121730</v>
+        <v>7121687</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -952,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165956</v>
+        <v>128165930</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,34 +2663,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729958</v>
+        <v>730154</v>
       </c>
       <c r="R22" t="n">
-        <v>7121839</v>
+        <v>7121446</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2723,6 +2727,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2749,7 +2758,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128165930</v>
+        <v>128165931</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2778,20 +2787,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730154</v>
+        <v>730017</v>
       </c>
       <c r="R23" t="n">
-        <v>7121446</v>
+        <v>7121813</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2828,7 +2833,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på samma tall</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2855,10 +2860,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165931</v>
+        <v>128165956</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2866,21 +2871,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2890,10 +2895,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730017</v>
+        <v>729958</v>
       </c>
       <c r="R24" t="n">
-        <v>7121813</v>
+        <v>7121839</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2926,11 +2931,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128221494</v>
+        <v>128221485</v>
       </c>
       <c r="B60" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,34 +6444,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730250</v>
+        <v>730021</v>
       </c>
       <c r="R60" t="n">
-        <v>7121538</v>
+        <v>7121603</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6512,6 +6515,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6530,10 +6534,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128221485</v>
+        <v>128221494</v>
       </c>
       <c r="B61" t="n">
-        <v>91352</v>
+        <v>80132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6541,37 +6545,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730021</v>
+        <v>730250</v>
       </c>
       <c r="R61" t="n">
-        <v>7121603</v>
+        <v>7121538</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6612,7 +6613,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165963</v>
+        <v>128165919</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730066</v>
+        <v>729911</v>
       </c>
       <c r="R2" t="n">
-        <v>7121525</v>
+        <v>7121731</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165947</v>
+        <v>128165938</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>80135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730042</v>
+        <v>729946</v>
       </c>
       <c r="R3" t="n">
-        <v>7121730</v>
+        <v>7121687</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -851,6 +859,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165938</v>
+        <v>128165963</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729946</v>
+        <v>730066</v>
       </c>
       <c r="R4" t="n">
-        <v>7121687</v>
+        <v>7121525</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -951,7 +957,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128165919</v>
+        <v>128165947</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729911</v>
+        <v>730042</v>
       </c>
       <c r="R5" t="n">
-        <v>7121731</v>
+        <v>7121730</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1041,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,7 +1075,7 @@
         <v>128165953</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128165945</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128165949</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128165950</v>
+        <v>128165970</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1392,16 +1392,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730039</v>
+        <v>730103</v>
       </c>
       <c r="R9" t="n">
-        <v>7121797</v>
+        <v>7121499</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1442,6 +1445,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1460,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128165972</v>
+        <v>128165950</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,19 +1493,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730154</v>
+        <v>730039</v>
       </c>
       <c r="R10" t="n">
-        <v>7121458</v>
+        <v>7121797</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1542,7 +1543,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128165970</v>
+        <v>128165972</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730103</v>
+        <v>730154</v>
       </c>
       <c r="R11" t="n">
-        <v>7121499</v>
+        <v>7121458</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1665,7 +1665,7 @@
         <v>128165954</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128165925</v>
       </c>
       <c r="B13" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128165943</v>
       </c>
       <c r="B14" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>128165944</v>
       </c>
       <c r="B15" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165935</v>
+        <v>128165922</v>
       </c>
       <c r="B16" t="n">
-        <v>97347</v>
+        <v>91325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2073,34 +2073,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730109</v>
+        <v>730083</v>
       </c>
       <c r="R16" t="n">
-        <v>7121506</v>
+        <v>7121514</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2141,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2159,48 +2163,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165922</v>
+        <v>128165946</v>
       </c>
       <c r="B17" t="n">
-        <v>91317</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730083</v>
+        <v>730160</v>
       </c>
       <c r="R17" t="n">
-        <v>7121514</v>
+        <v>7121748</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2241,7 +2242,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128165962</v>
+        <v>128165961</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729916</v>
+        <v>729905</v>
       </c>
       <c r="R18" t="n">
-        <v>7121715</v>
+        <v>7121772</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128165946</v>
+        <v>128165962</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730160</v>
+        <v>729916</v>
       </c>
       <c r="R19" t="n">
-        <v>7121748</v>
+        <v>7121715</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128165961</v>
+        <v>128165935</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>97355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>729905</v>
+        <v>730109</v>
       </c>
       <c r="R20" t="n">
-        <v>7121772</v>
+        <v>7121506</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2554,7 +2554,7 @@
         <v>128165960</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165930</v>
+        <v>128165956</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,38 +2663,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730154</v>
+        <v>729958</v>
       </c>
       <c r="R22" t="n">
-        <v>7121446</v>
+        <v>7121839</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2727,11 +2723,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2761,7 +2752,7 @@
         <v>128165931</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2860,10 +2851,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165956</v>
+        <v>128165930</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2871,34 +2862,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729958</v>
+        <v>730154</v>
       </c>
       <c r="R24" t="n">
-        <v>7121839</v>
+        <v>7121446</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2931,6 +2926,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2960,7 +2960,7 @@
         <v>128165974</v>
       </c>
       <c r="B25" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128165951</v>
+        <v>128165959</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730024</v>
+        <v>729945</v>
       </c>
       <c r="R26" t="n">
-        <v>7121785</v>
+        <v>7121797</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128165959</v>
+        <v>128165951</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729945</v>
+        <v>730024</v>
       </c>
       <c r="R27" t="n">
-        <v>7121797</v>
+        <v>7121785</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3251,7 +3251,7 @@
         <v>128165926</v>
       </c>
       <c r="B28" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128165969</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>128165955</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>128165933</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128165932</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>128165934</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>128165957</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>128165948</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>128165967</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>128165971</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>128165928</v>
       </c>
       <c r="B38" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128165965</v>
+        <v>128165958</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4379,19 +4379,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730086</v>
+        <v>729942</v>
       </c>
       <c r="R39" t="n">
-        <v>7121516</v>
+        <v>7121803</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4432,7 +4429,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4451,10 +4447,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128165958</v>
+        <v>128165965</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4480,16 +4476,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729942</v>
+        <v>730086</v>
       </c>
       <c r="R40" t="n">
-        <v>7121803</v>
+        <v>7121516</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4530,6 +4529,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>128165927</v>
       </c>
       <c r="B41" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>128165942</v>
       </c>
       <c r="B42" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>128165939</v>
       </c>
       <c r="B43" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>128221493</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5043,10 +5043,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128221496</v>
+        <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5078,10 +5078,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730168</v>
+        <v>730112</v>
       </c>
       <c r="R46" t="n">
-        <v>7121738</v>
+        <v>7121785</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5122,7 +5122,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5141,10 +5140,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128221497</v>
+        <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5176,10 +5175,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730112</v>
+        <v>730168</v>
       </c>
       <c r="R47" t="n">
-        <v>7121785</v>
+        <v>7121738</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5220,6 +5219,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>128221495</v>
       </c>
       <c r="B48" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128221503</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221484</v>
       </c>
       <c r="B50" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221481</v>
       </c>
       <c r="B51" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5631,48 +5631,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B52" t="n">
-        <v>91317</v>
+        <v>98478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R52" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5710,74 +5718,67 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>91325</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R53" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5815,19 +5816,18 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6032,56 +6032,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128165941</v>
+        <v>128221489</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>57670</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729946</v>
+        <v>730051</v>
       </c>
       <c r="R56" t="n">
-        <v>7121788</v>
+        <v>7121646</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6119,67 +6111,74 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128221489</v>
+        <v>128165941</v>
       </c>
       <c r="B57" t="n">
-        <v>57669</v>
+        <v>98478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730051</v>
+        <v>729946</v>
       </c>
       <c r="R57" t="n">
-        <v>7121646</v>
+        <v>7121788</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6217,66 +6216,64 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221486</v>
+        <v>128221500</v>
       </c>
       <c r="B58" t="n">
-        <v>91352</v>
+        <v>98478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730186</v>
+        <v>730091</v>
       </c>
       <c r="R58" t="n">
-        <v>7121516</v>
+        <v>7121561</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6317,7 +6314,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6336,45 +6332,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221500</v>
+        <v>128221486</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>91360</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730091</v>
+        <v>730186</v>
       </c>
       <c r="R59" t="n">
-        <v>7121561</v>
+        <v>7121516</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6415,6 +6414,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>128221485</v>
       </c>
       <c r="B60" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128221494</v>
       </c>
       <c r="B61" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6631,32 +6631,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128221480</v>
+        <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91317</v>
+        <v>91378</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730261</v>
+        <v>730247</v>
       </c>
       <c r="R62" t="n">
-        <v>7121621</v>
+        <v>7121509</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6728,32 +6728,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128221502</v>
+        <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91370</v>
+        <v>91325</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730247</v>
+        <v>730261</v>
       </c>
       <c r="R63" t="n">
-        <v>7121509</v>
+        <v>7121621</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165956</v>
+        <v>128165931</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,21 +2663,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729958</v>
+        <v>730017</v>
       </c>
       <c r="R22" t="n">
-        <v>7121839</v>
+        <v>7121813</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2723,6 +2723,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2749,7 +2754,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128165931</v>
+        <v>128165930</v>
       </c>
       <c r="B23" t="n">
         <v>57673</v>
@@ -2778,16 +2783,20 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730017</v>
+        <v>730154</v>
       </c>
       <c r="R23" t="n">
-        <v>7121813</v>
+        <v>7121446</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2824,7 +2833,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2851,10 +2860,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165930</v>
+        <v>128165956</v>
       </c>
       <c r="B24" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2862,38 +2871,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730154</v>
+        <v>729958</v>
       </c>
       <c r="R24" t="n">
-        <v>7121446</v>
+        <v>7121839</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2926,11 +2931,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165919</v>
+        <v>128165963</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729911</v>
+        <v>730066</v>
       </c>
       <c r="R2" t="n">
-        <v>7121731</v>
+        <v>7121525</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165938</v>
+        <v>128165947</v>
       </c>
       <c r="B3" t="n">
-        <v>80135</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729946</v>
+        <v>730042</v>
       </c>
       <c r="R3" t="n">
-        <v>7121687</v>
+        <v>7121730</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -859,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165963</v>
+        <v>128165938</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730066</v>
+        <v>729946</v>
       </c>
       <c r="R4" t="n">
-        <v>7121525</v>
+        <v>7121687</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -957,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -975,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128165947</v>
+        <v>128165919</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730042</v>
+        <v>729911</v>
       </c>
       <c r="R5" t="n">
-        <v>7121730</v>
+        <v>7121731</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1046,6 +1041,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,7 +1075,7 @@
         <v>128165953</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128165945</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128165949</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128165970</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>128165950</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>128165972</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>128165954</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128165925</v>
       </c>
       <c r="B13" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128165943</v>
       </c>
       <c r="B14" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>128165944</v>
       </c>
       <c r="B15" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,48 +2062,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165922</v>
+        <v>128165946</v>
       </c>
       <c r="B16" t="n">
-        <v>91325</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730083</v>
+        <v>730160</v>
       </c>
       <c r="R16" t="n">
-        <v>7121514</v>
+        <v>7121748</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2144,7 +2141,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,10 +2159,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165946</v>
+        <v>128165961</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,10 +2194,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730160</v>
+        <v>729905</v>
       </c>
       <c r="R17" t="n">
-        <v>7121748</v>
+        <v>7121772</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2260,10 +2256,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128165961</v>
+        <v>128165962</v>
       </c>
       <c r="B18" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2295,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729905</v>
+        <v>729916</v>
       </c>
       <c r="R18" t="n">
-        <v>7121772</v>
+        <v>7121715</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2357,45 +2353,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128165962</v>
+        <v>128165922</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>91417</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>729916</v>
+        <v>730083</v>
       </c>
       <c r="R19" t="n">
-        <v>7121715</v>
+        <v>7121514</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2436,6 +2435,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>128165935</v>
       </c>
       <c r="B20" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>128165960</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165931</v>
+        <v>128165956</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,21 +2663,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730017</v>
+        <v>729958</v>
       </c>
       <c r="R22" t="n">
-        <v>7121813</v>
+        <v>7121839</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2723,11 +2723,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,7 +2752,7 @@
         <v>128165930</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2860,10 +2855,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165956</v>
+        <v>128165931</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2871,21 +2866,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2895,10 +2890,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729958</v>
+        <v>730017</v>
       </c>
       <c r="R24" t="n">
-        <v>7121839</v>
+        <v>7121813</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2931,6 +2926,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2960,7 +2960,7 @@
         <v>128165974</v>
       </c>
       <c r="B25" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>128165959</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>128165951</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>128165926</v>
       </c>
       <c r="B28" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128165969</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>128165955</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>128165933</v>
       </c>
       <c r="B31" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128165932</v>
       </c>
       <c r="B32" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>128165934</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>128165957</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>128165948</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>128165967</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>128165971</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>128165928</v>
       </c>
       <c r="B38" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128165958</v>
+        <v>128165927</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>91452</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4361,21 +4361,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729942</v>
+        <v>730137</v>
       </c>
       <c r="R39" t="n">
-        <v>7121803</v>
+        <v>7121478</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128165965</v>
+        <v>128165958</v>
       </c>
       <c r="B40" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4476,19 +4476,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730086</v>
+        <v>729942</v>
       </c>
       <c r="R40" t="n">
-        <v>7121516</v>
+        <v>7121803</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4529,7 +4526,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4548,10 +4544,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128165927</v>
+        <v>128165965</v>
       </c>
       <c r="B41" t="n">
-        <v>91360</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4559,34 +4555,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730137</v>
+        <v>730086</v>
       </c>
       <c r="R41" t="n">
-        <v>7121478</v>
+        <v>7121516</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4627,6 +4626,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4648,7 +4648,7 @@
         <v>128165942</v>
       </c>
       <c r="B42" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>128165939</v>
       </c>
       <c r="B43" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>128221493</v>
       </c>
       <c r="B45" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5238,10 +5238,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128221495</v>
+        <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>80135</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5249,21 +5249,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730262</v>
+        <v>730239</v>
       </c>
       <c r="R48" t="n">
-        <v>7121551</v>
+        <v>7121592</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5309,6 +5309,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5335,10 +5340,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128221503</v>
+        <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5346,21 +5351,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5370,10 +5375,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730239</v>
+        <v>730262</v>
       </c>
       <c r="R49" t="n">
-        <v>7121592</v>
+        <v>7121551</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5406,11 +5411,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5440,7 +5440,7 @@
         <v>128221484</v>
       </c>
       <c r="B50" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221481</v>
       </c>
       <c r="B51" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5631,56 +5631,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>98478</v>
+        <v>91417</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R52" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5718,67 +5710,74 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B53" t="n">
-        <v>91325</v>
+        <v>98571</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R53" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5816,18 +5815,19 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6032,48 +6032,56 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128221489</v>
+        <v>128165941</v>
       </c>
       <c r="B56" t="n">
-        <v>57670</v>
+        <v>98571</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730051</v>
+        <v>729946</v>
       </c>
       <c r="R56" t="n">
-        <v>7121646</v>
+        <v>7121788</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6111,74 +6119,67 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128165941</v>
+        <v>128221489</v>
       </c>
       <c r="B57" t="n">
-        <v>98478</v>
+        <v>57682</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729946</v>
+        <v>730051</v>
       </c>
       <c r="R57" t="n">
-        <v>7121788</v>
+        <v>7121646</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6216,64 +6217,66 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221500</v>
+        <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>98478</v>
+        <v>91452</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730091</v>
+        <v>730186</v>
       </c>
       <c r="R58" t="n">
-        <v>7121561</v>
+        <v>7121516</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6314,6 +6317,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6332,48 +6336,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221486</v>
+        <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>91360</v>
+        <v>98571</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730186</v>
+        <v>730091</v>
       </c>
       <c r="R59" t="n">
-        <v>7121516</v>
+        <v>7121561</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6414,7 +6415,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>128221485</v>
       </c>
       <c r="B60" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128221494</v>
       </c>
       <c r="B61" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -1759,10 +1759,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128165925</v>
+        <v>128165943</v>
       </c>
       <c r="B13" t="n">
-        <v>91452</v>
+        <v>91470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730049</v>
+        <v>730059</v>
       </c>
       <c r="R13" t="n">
-        <v>7121812</v>
+        <v>7121540</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128165943</v>
+        <v>128165925</v>
       </c>
       <c r="B14" t="n">
-        <v>91470</v>
+        <v>91452</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730059</v>
+        <v>730049</v>
       </c>
       <c r="R14" t="n">
-        <v>7121540</v>
+        <v>7121812</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128165926</v>
+        <v>128165969</v>
       </c>
       <c r="B28" t="n">
-        <v>91452</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3259,34 +3259,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730131</v>
+        <v>730111</v>
       </c>
       <c r="R28" t="n">
-        <v>7121481</v>
+        <v>7121506</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3327,6 +3330,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3345,10 +3349,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128165969</v>
+        <v>128165926</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3356,37 +3360,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730111</v>
+        <v>730131</v>
       </c>
       <c r="R29" t="n">
-        <v>7121506</v>
+        <v>7121481</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3427,7 +3428,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128165955</v>
+        <v>128165932</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3457,21 +3457,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>729973</v>
+        <v>730083</v>
       </c>
       <c r="R30" t="n">
-        <v>7121813</v>
+        <v>7121500</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3517,6 +3517,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3649,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128165932</v>
+        <v>128165955</v>
       </c>
       <c r="B32" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,21 +3665,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3684,10 +3689,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730083</v>
+        <v>729973</v>
       </c>
       <c r="R32" t="n">
-        <v>7121500</v>
+        <v>7121813</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3720,11 +3725,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4447,10 +4447,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128165958</v>
+        <v>128165942</v>
       </c>
       <c r="B40" t="n">
-        <v>79083</v>
+        <v>91470</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4458,21 +4458,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729942</v>
+        <v>730136</v>
       </c>
       <c r="R40" t="n">
-        <v>7121803</v>
+        <v>7121772</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4544,7 +4544,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128165965</v>
+        <v>128165958</v>
       </c>
       <c r="B41" t="n">
         <v>79083</v>
@@ -4573,19 +4573,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730086</v>
+        <v>729942</v>
       </c>
       <c r="R41" t="n">
-        <v>7121516</v>
+        <v>7121803</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4626,7 +4623,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4645,10 +4641,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128165942</v>
+        <v>128165965</v>
       </c>
       <c r="B42" t="n">
-        <v>91470</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4656,34 +4652,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730136</v>
+        <v>730086</v>
       </c>
       <c r="R42" t="n">
-        <v>7121772</v>
+        <v>7121516</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4724,6 +4723,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6631,32 +6631,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128221502</v>
+        <v>128221498</v>
       </c>
       <c r="B62" t="n">
-        <v>91470</v>
+        <v>98571</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730247</v>
+        <v>730083</v>
       </c>
       <c r="R62" t="n">
-        <v>7121509</v>
+        <v>7121587</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6728,32 +6728,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128221480</v>
+        <v>128221502</v>
       </c>
       <c r="B63" t="n">
-        <v>91417</v>
+        <v>91470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730261</v>
+        <v>730247</v>
       </c>
       <c r="R63" t="n">
-        <v>7121621</v>
+        <v>7121509</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6825,32 +6825,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128221498</v>
+        <v>128221480</v>
       </c>
       <c r="B64" t="n">
-        <v>98571</v>
+        <v>91417</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>730083</v>
+        <v>730261</v>
       </c>
       <c r="R64" t="n">
-        <v>7121587</v>
+        <v>7121621</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165963</v>
+        <v>128165938</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730066</v>
+        <v>729946</v>
       </c>
       <c r="R2" t="n">
-        <v>7121525</v>
+        <v>7121687</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165947</v>
+        <v>128165919</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730042</v>
+        <v>729911</v>
       </c>
       <c r="R3" t="n">
-        <v>7121730</v>
+        <v>7121731</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -843,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165938</v>
+        <v>128165963</v>
       </c>
       <c r="B4" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729946</v>
+        <v>730066</v>
       </c>
       <c r="R4" t="n">
-        <v>7121687</v>
+        <v>7121525</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -951,7 +957,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128165919</v>
+        <v>128165947</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729911</v>
+        <v>730042</v>
       </c>
       <c r="R5" t="n">
-        <v>7121731</v>
+        <v>7121730</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1041,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2062,32 +2062,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165946</v>
+        <v>128165935</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>97448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730160</v>
+        <v>730109</v>
       </c>
       <c r="R16" t="n">
-        <v>7121748</v>
+        <v>7121506</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165961</v>
+        <v>128165946</v>
       </c>
       <c r="B17" t="n">
         <v>79083</v>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729905</v>
+        <v>730160</v>
       </c>
       <c r="R17" t="n">
-        <v>7121772</v>
+        <v>7121748</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128165962</v>
+        <v>128165961</v>
       </c>
       <c r="B18" t="n">
         <v>79083</v>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729916</v>
+        <v>729905</v>
       </c>
       <c r="R18" t="n">
-        <v>7121715</v>
+        <v>7121772</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128165935</v>
+        <v>128165962</v>
       </c>
       <c r="B20" t="n">
-        <v>97448</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730109</v>
+        <v>729916</v>
       </c>
       <c r="R20" t="n">
-        <v>7121506</v>
+        <v>7121715</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128165969</v>
+        <v>128165926</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3259,37 +3259,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730111</v>
+        <v>730131</v>
       </c>
       <c r="R28" t="n">
-        <v>7121506</v>
+        <v>7121481</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3330,7 +3327,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3349,10 +3345,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128165926</v>
+        <v>128165969</v>
       </c>
       <c r="B29" t="n">
-        <v>91452</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3360,34 +3356,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730131</v>
+        <v>730111</v>
       </c>
       <c r="R29" t="n">
-        <v>7121481</v>
+        <v>7121506</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3428,6 +3427,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128165932</v>
+        <v>128165955</v>
       </c>
       <c r="B30" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3457,21 +3457,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730083</v>
+        <v>729973</v>
       </c>
       <c r="R30" t="n">
-        <v>7121500</v>
+        <v>7121813</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3517,11 +3517,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3654,10 +3649,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128165955</v>
+        <v>128165932</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,21 +3660,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,10 +3684,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>729973</v>
+        <v>730083</v>
       </c>
       <c r="R32" t="n">
-        <v>7121813</v>
+        <v>7121500</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,6 +3720,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5238,10 +5238,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128221503</v>
+        <v>128221495</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5249,21 +5249,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730239</v>
+        <v>730262</v>
       </c>
       <c r="R48" t="n">
-        <v>7121592</v>
+        <v>7121551</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5309,11 +5309,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5340,10 +5335,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128221495</v>
+        <v>128221503</v>
       </c>
       <c r="B49" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5351,21 +5346,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5375,10 +5370,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730262</v>
+        <v>730239</v>
       </c>
       <c r="R49" t="n">
-        <v>7121551</v>
+        <v>7121592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5411,6 +5406,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5437,32 +5437,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128221484</v>
+        <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91452</v>
+        <v>91417</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730055</v>
+        <v>730240</v>
       </c>
       <c r="R50" t="n">
-        <v>7121821</v>
+        <v>7121639</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5534,32 +5534,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128221481</v>
+        <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91417</v>
+        <v>91452</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730240</v>
+        <v>730055</v>
       </c>
       <c r="R51" t="n">
-        <v>7121639</v>
+        <v>7121821</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5631,48 +5631,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B52" t="n">
-        <v>91417</v>
+        <v>98571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R52" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5710,74 +5718,67 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B53" t="n">
-        <v>98571</v>
+        <v>91417</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R53" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5815,29 +5816,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128221482</v>
+        <v>128221487</v>
       </c>
       <c r="B54" t="n">
-        <v>91417</v>
+        <v>80217</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,37 +5845,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730021</v>
+        <v>730102</v>
       </c>
       <c r="R54" t="n">
-        <v>7121603</v>
+        <v>7121795</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5916,7 +5913,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5935,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128221487</v>
+        <v>128221482</v>
       </c>
       <c r="B55" t="n">
-        <v>80217</v>
+        <v>91417</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5946,34 +5942,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730102</v>
+        <v>730021</v>
       </c>
       <c r="R55" t="n">
-        <v>7121795</v>
+        <v>7121603</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6014,6 +6013,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6032,56 +6032,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128165941</v>
+        <v>128221489</v>
       </c>
       <c r="B56" t="n">
-        <v>98571</v>
+        <v>57682</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729946</v>
+        <v>730051</v>
       </c>
       <c r="R56" t="n">
-        <v>7121788</v>
+        <v>7121646</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6119,67 +6111,74 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128221489</v>
+        <v>128165941</v>
       </c>
       <c r="B57" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730051</v>
+        <v>729946</v>
       </c>
       <c r="R57" t="n">
-        <v>7121646</v>
+        <v>7121788</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6217,66 +6216,64 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221486</v>
+        <v>128221500</v>
       </c>
       <c r="B58" t="n">
-        <v>91452</v>
+        <v>98571</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730186</v>
+        <v>730091</v>
       </c>
       <c r="R58" t="n">
-        <v>7121516</v>
+        <v>7121561</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6317,7 +6314,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6336,45 +6332,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221500</v>
+        <v>128221486</v>
       </c>
       <c r="B59" t="n">
-        <v>98571</v>
+        <v>91452</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730091</v>
+        <v>730186</v>
       </c>
       <c r="R59" t="n">
-        <v>7121561</v>
+        <v>7121516</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6415,6 +6414,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6631,32 +6631,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128221498</v>
+        <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>98571</v>
+        <v>91470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730083</v>
+        <v>730247</v>
       </c>
       <c r="R62" t="n">
-        <v>7121587</v>
+        <v>7121509</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6728,32 +6728,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128221502</v>
+        <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91470</v>
+        <v>91417</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730247</v>
+        <v>730261</v>
       </c>
       <c r="R63" t="n">
-        <v>7121509</v>
+        <v>7121621</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6825,32 +6825,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128221480</v>
+        <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>91417</v>
+        <v>98571</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>730261</v>
+        <v>730083</v>
       </c>
       <c r="R64" t="n">
-        <v>7121621</v>
+        <v>7121587</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165938</v>
+        <v>128165919</v>
       </c>
       <c r="B2" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729946</v>
+        <v>729911</v>
       </c>
       <c r="R2" t="n">
-        <v>7121687</v>
+        <v>7121731</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,13 +748,17 @@
           <t>2025-09-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165919</v>
+        <v>128165963</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729911</v>
+        <v>730066</v>
       </c>
       <c r="R3" t="n">
-        <v>7121731</v>
+        <v>7121525</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -847,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165963</v>
+        <v>128165947</v>
       </c>
       <c r="B4" t="n">
         <v>79083</v>
@@ -913,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730066</v>
+        <v>730042</v>
       </c>
       <c r="R4" t="n">
-        <v>7121525</v>
+        <v>7121730</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -975,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128165947</v>
+        <v>128165938</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,34 +982,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730042</v>
+        <v>729946</v>
       </c>
       <c r="R5" t="n">
-        <v>7121730</v>
+        <v>7121687</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1054,6 +1053,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128165943</v>
+        <v>128165925</v>
       </c>
       <c r="B13" t="n">
-        <v>91470</v>
+        <v>91452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730059</v>
+        <v>730049</v>
       </c>
       <c r="R13" t="n">
-        <v>7121540</v>
+        <v>7121812</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128165925</v>
+        <v>128165943</v>
       </c>
       <c r="B14" t="n">
-        <v>91452</v>
+        <v>91470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730049</v>
+        <v>730059</v>
       </c>
       <c r="R14" t="n">
-        <v>7121812</v>
+        <v>7121540</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2062,32 +2062,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165935</v>
+        <v>128165946</v>
       </c>
       <c r="B16" t="n">
-        <v>97448</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730109</v>
+        <v>730160</v>
       </c>
       <c r="R16" t="n">
-        <v>7121506</v>
+        <v>7121748</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165946</v>
+        <v>128165961</v>
       </c>
       <c r="B17" t="n">
         <v>79083</v>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730160</v>
+        <v>729905</v>
       </c>
       <c r="R17" t="n">
-        <v>7121748</v>
+        <v>7121772</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2256,45 +2256,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128165961</v>
+        <v>128165922</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>91417</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729905</v>
+        <v>730083</v>
       </c>
       <c r="R18" t="n">
-        <v>7121772</v>
+        <v>7121514</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2335,6 +2338,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2353,48 +2357,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128165922</v>
+        <v>128165962</v>
       </c>
       <c r="B19" t="n">
-        <v>91417</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730083</v>
+        <v>729916</v>
       </c>
       <c r="R19" t="n">
-        <v>7121514</v>
+        <v>7121715</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2435,7 +2436,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128165962</v>
+        <v>128165935</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>97448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>729916</v>
+        <v>730109</v>
       </c>
       <c r="R20" t="n">
-        <v>7121715</v>
+        <v>7121506</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128221481</v>
+        <v>128221484</v>
       </c>
       <c r="B50" t="n">
-        <v>91417</v>
+        <v>91452</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730240</v>
+        <v>730055</v>
       </c>
       <c r="R50" t="n">
-        <v>7121639</v>
+        <v>7121821</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5534,32 +5534,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128221484</v>
+        <v>128221481</v>
       </c>
       <c r="B51" t="n">
-        <v>91452</v>
+        <v>91417</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730055</v>
+        <v>730240</v>
       </c>
       <c r="R51" t="n">
-        <v>7121821</v>
+        <v>7121639</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5631,56 +5631,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>98571</v>
+        <v>91417</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R52" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5718,67 +5710,74 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B53" t="n">
-        <v>91417</v>
+        <v>98571</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R53" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5816,28 +5815,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128221487</v>
+        <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>80217</v>
+        <v>91417</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,34 +5845,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730102</v>
+        <v>730021</v>
       </c>
       <c r="R54" t="n">
-        <v>7121795</v>
+        <v>7121603</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5913,6 +5916,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5931,10 +5935,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128221482</v>
+        <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>91417</v>
+        <v>80217</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,37 +5946,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730021</v>
+        <v>730102</v>
       </c>
       <c r="R55" t="n">
-        <v>7121603</v>
+        <v>7121795</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6013,7 +6014,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165919</v>
+        <v>128165963</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729911</v>
+        <v>730066</v>
       </c>
       <c r="R2" t="n">
-        <v>7121731</v>
+        <v>7121525</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165963</v>
+        <v>128165947</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730066</v>
+        <v>730042</v>
       </c>
       <c r="R3" t="n">
-        <v>7121525</v>
+        <v>7121730</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165947</v>
+        <v>128165938</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>80192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730042</v>
+        <v>729946</v>
       </c>
       <c r="R4" t="n">
-        <v>7121730</v>
+        <v>7121687</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -953,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -971,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128165938</v>
+        <v>128165919</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,37 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729946</v>
+        <v>729911</v>
       </c>
       <c r="R5" t="n">
-        <v>7121687</v>
+        <v>7121731</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1047,13 +1043,17 @@
           <t>2025-09-01</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>128165953</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128165945</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128165949</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128165970</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>128165950</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>128165972</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>128165954</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128165925</v>
+        <v>128165943</v>
       </c>
       <c r="B13" t="n">
-        <v>91452</v>
+        <v>91482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730049</v>
+        <v>730059</v>
       </c>
       <c r="R13" t="n">
-        <v>7121812</v>
+        <v>7121540</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128165943</v>
+        <v>128165925</v>
       </c>
       <c r="B14" t="n">
-        <v>91470</v>
+        <v>91464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730059</v>
+        <v>730049</v>
       </c>
       <c r="R14" t="n">
-        <v>7121540</v>
+        <v>7121812</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1964,7 +1964,7 @@
         <v>128165944</v>
       </c>
       <c r="B15" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>128165946</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>128165961</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,48 +2256,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128165922</v>
+        <v>128165962</v>
       </c>
       <c r="B18" t="n">
-        <v>91417</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730083</v>
+        <v>729916</v>
       </c>
       <c r="R18" t="n">
-        <v>7121514</v>
+        <v>7121715</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2338,7 +2335,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2357,45 +2353,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128165962</v>
+        <v>128165922</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>91429</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>729916</v>
+        <v>730083</v>
       </c>
       <c r="R19" t="n">
-        <v>7121715</v>
+        <v>7121514</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2436,6 +2435,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>128165935</v>
       </c>
       <c r="B20" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>128165960</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>128165956</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>128165930</v>
       </c>
       <c r="B23" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>128165931</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>128165974</v>
       </c>
       <c r="B25" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>128165959</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>128165951</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>128165926</v>
       </c>
       <c r="B28" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128165969</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>128165955</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>128165933</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128165932</v>
       </c>
       <c r="B32" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>128165934</v>
       </c>
       <c r="B33" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>128165957</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>128165948</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>128165967</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>128165971</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>128165928</v>
       </c>
       <c r="B38" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128165927</v>
+        <v>128165942</v>
       </c>
       <c r="B39" t="n">
-        <v>91452</v>
+        <v>91482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4361,21 +4361,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730137</v>
+        <v>730136</v>
       </c>
       <c r="R39" t="n">
-        <v>7121478</v>
+        <v>7121772</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128165942</v>
+        <v>128165927</v>
       </c>
       <c r="B40" t="n">
-        <v>91470</v>
+        <v>91464</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4458,21 +4458,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730136</v>
+        <v>730137</v>
       </c>
       <c r="R40" t="n">
-        <v>7121772</v>
+        <v>7121478</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4547,7 +4547,7 @@
         <v>128165958</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>128165965</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>128165939</v>
       </c>
       <c r="B43" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91748</v>
+        <v>91760</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>128221493</v>
       </c>
       <c r="B45" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128221495</v>
       </c>
       <c r="B48" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128221503</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221484</v>
       </c>
       <c r="B50" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221481</v>
       </c>
       <c r="B51" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5631,48 +5631,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B52" t="n">
-        <v>91417</v>
+        <v>98585</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R52" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5710,74 +5718,67 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B53" t="n">
-        <v>98571</v>
+        <v>91429</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R53" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5815,29 +5816,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128221482</v>
+        <v>128221487</v>
       </c>
       <c r="B54" t="n">
-        <v>91417</v>
+        <v>80221</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,37 +5845,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730021</v>
+        <v>730102</v>
       </c>
       <c r="R54" t="n">
-        <v>7121603</v>
+        <v>7121795</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5916,7 +5913,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5935,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128221487</v>
+        <v>128221482</v>
       </c>
       <c r="B55" t="n">
-        <v>80217</v>
+        <v>91429</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5946,34 +5942,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730102</v>
+        <v>730021</v>
       </c>
       <c r="R55" t="n">
-        <v>7121795</v>
+        <v>7121603</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6014,6 +6013,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6032,48 +6032,56 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128221489</v>
+        <v>128165941</v>
       </c>
       <c r="B56" t="n">
-        <v>57682</v>
+        <v>98585</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730051</v>
+        <v>729946</v>
       </c>
       <c r="R56" t="n">
-        <v>7121646</v>
+        <v>7121788</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6111,74 +6119,67 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128165941</v>
+        <v>128221489</v>
       </c>
       <c r="B57" t="n">
-        <v>98571</v>
+        <v>57686</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729946</v>
+        <v>730051</v>
       </c>
       <c r="R57" t="n">
-        <v>7121788</v>
+        <v>7121646</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6216,64 +6217,66 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221500</v>
+        <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>98571</v>
+        <v>91464</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730091</v>
+        <v>730186</v>
       </c>
       <c r="R58" t="n">
-        <v>7121561</v>
+        <v>7121516</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6314,6 +6317,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6332,48 +6336,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221486</v>
+        <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>91452</v>
+        <v>98585</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730186</v>
+        <v>730091</v>
       </c>
       <c r="R59" t="n">
-        <v>7121516</v>
+        <v>7121561</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6414,7 +6415,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>128221485</v>
       </c>
       <c r="B60" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128221494</v>
       </c>
       <c r="B61" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96823</v>
+        <v>96835</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -5437,32 +5437,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128221484</v>
+        <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91464</v>
+        <v>91429</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730055</v>
+        <v>730240</v>
       </c>
       <c r="R50" t="n">
-        <v>7121821</v>
+        <v>7121639</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5534,32 +5534,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128221481</v>
+        <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91429</v>
+        <v>91464</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730240</v>
+        <v>730055</v>
       </c>
       <c r="R51" t="n">
-        <v>7121639</v>
+        <v>7121821</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128165963</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128165947</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128165938</v>
       </c>
       <c r="B4" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128165953</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128165945</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128165949</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128165970</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>128165950</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>128165972</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>128165954</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128165943</v>
       </c>
       <c r="B13" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128165925</v>
       </c>
       <c r="B14" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>128165944</v>
       </c>
       <c r="B15" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>128165946</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>128165961</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>128165962</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128165922</v>
       </c>
       <c r="B19" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>128165935</v>
       </c>
       <c r="B20" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>128165960</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>128165956</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>128165974</v>
       </c>
       <c r="B25" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>128165959</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>128165951</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>128165926</v>
       </c>
       <c r="B28" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128165969</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>128165955</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128165957</v>
+        <v>128165948</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>729953</v>
+        <v>730039</v>
       </c>
       <c r="R34" t="n">
-        <v>7121824</v>
+        <v>7121748</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128165948</v>
+        <v>128165957</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730039</v>
+        <v>729953</v>
       </c>
       <c r="R35" t="n">
-        <v>7121748</v>
+        <v>7121824</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4050,7 +4050,7 @@
         <v>128165967</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>128165971</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>128165928</v>
       </c>
       <c r="B38" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128165942</v>
+        <v>128165927</v>
       </c>
       <c r="B39" t="n">
-        <v>91482</v>
+        <v>91466</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4361,21 +4361,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730136</v>
+        <v>730137</v>
       </c>
       <c r="R39" t="n">
-        <v>7121772</v>
+        <v>7121478</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128165927</v>
+        <v>128165942</v>
       </c>
       <c r="B40" t="n">
-        <v>91464</v>
+        <v>91484</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4458,21 +4458,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730137</v>
+        <v>730136</v>
       </c>
       <c r="R40" t="n">
-        <v>7121478</v>
+        <v>7121772</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4547,7 +4547,7 @@
         <v>128165958</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>128165965</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>128165939</v>
       </c>
       <c r="B43" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128221495</v>
       </c>
       <c r="B48" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128221503</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128165940</v>
       </c>
       <c r="B52" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>128221483</v>
       </c>
       <c r="B53" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128221487</v>
+        <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>80221</v>
+        <v>91431</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,34 +5845,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730102</v>
+        <v>730021</v>
       </c>
       <c r="R54" t="n">
-        <v>7121795</v>
+        <v>7121603</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5913,6 +5916,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5931,10 +5935,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128221482</v>
+        <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>91429</v>
+        <v>80223</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,37 +5946,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730021</v>
+        <v>730102</v>
       </c>
       <c r="R55" t="n">
-        <v>7121603</v>
+        <v>7121795</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6013,7 +6014,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6035,7 +6035,7 @@
         <v>128165941</v>
       </c>
       <c r="B56" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128221485</v>
+        <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>91464</v>
+        <v>80194</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,37 +6444,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730021</v>
+        <v>730250</v>
       </c>
       <c r="R60" t="n">
-        <v>7121603</v>
+        <v>7121538</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6515,7 +6512,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6534,10 +6530,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128221494</v>
+        <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>80192</v>
+        <v>91466</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6545,34 +6541,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730250</v>
+        <v>730021</v>
       </c>
       <c r="R61" t="n">
-        <v>7121538</v>
+        <v>7121603</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6613,6 +6612,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6631,32 +6631,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128221502</v>
+        <v>128221498</v>
       </c>
       <c r="B62" t="n">
-        <v>91482</v>
+        <v>98588</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730247</v>
+        <v>730083</v>
       </c>
       <c r="R62" t="n">
-        <v>7121509</v>
+        <v>7121587</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6728,32 +6728,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128221480</v>
+        <v>128221502</v>
       </c>
       <c r="B63" t="n">
-        <v>91429</v>
+        <v>91484</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730261</v>
+        <v>730247</v>
       </c>
       <c r="R63" t="n">
-        <v>7121621</v>
+        <v>7121509</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6825,32 +6825,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128221498</v>
+        <v>128221480</v>
       </c>
       <c r="B64" t="n">
-        <v>98585</v>
+        <v>91431</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>730083</v>
+        <v>730261</v>
       </c>
       <c r="R64" t="n">
-        <v>7121587</v>
+        <v>7121621</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165963</v>
+        <v>128165938</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730066</v>
+        <v>729946</v>
       </c>
       <c r="R2" t="n">
-        <v>7121525</v>
+        <v>7121687</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165947</v>
+        <v>128165919</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730042</v>
+        <v>729911</v>
       </c>
       <c r="R3" t="n">
-        <v>7121730</v>
+        <v>7121731</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -843,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165938</v>
+        <v>128165963</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729946</v>
+        <v>730066</v>
       </c>
       <c r="R4" t="n">
-        <v>7121687</v>
+        <v>7121525</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -951,7 +957,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128165919</v>
+        <v>128165947</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729911</v>
+        <v>730042</v>
       </c>
       <c r="R5" t="n">
-        <v>7121731</v>
+        <v>7121730</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1041,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1759,10 +1759,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128165943</v>
+        <v>128165925</v>
       </c>
       <c r="B13" t="n">
-        <v>91484</v>
+        <v>91466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730059</v>
+        <v>730049</v>
       </c>
       <c r="R13" t="n">
-        <v>7121540</v>
+        <v>7121812</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128165925</v>
+        <v>128165943</v>
       </c>
       <c r="B14" t="n">
-        <v>91466</v>
+        <v>91484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730049</v>
+        <v>730059</v>
       </c>
       <c r="R14" t="n">
-        <v>7121812</v>
+        <v>7121540</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2062,45 +2062,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165946</v>
+        <v>128165922</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>91431</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730160</v>
+        <v>730083</v>
       </c>
       <c r="R16" t="n">
-        <v>7121748</v>
+        <v>7121514</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2141,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2159,7 +2163,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165961</v>
+        <v>128165946</v>
       </c>
       <c r="B17" t="n">
         <v>79089</v>
@@ -2194,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729905</v>
+        <v>730160</v>
       </c>
       <c r="R17" t="n">
-        <v>7121772</v>
+        <v>7121748</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2256,7 +2260,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128165962</v>
+        <v>128165961</v>
       </c>
       <c r="B18" t="n">
         <v>79089</v>
@@ -2291,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729916</v>
+        <v>729905</v>
       </c>
       <c r="R18" t="n">
-        <v>7121715</v>
+        <v>7121772</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2353,48 +2357,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128165922</v>
+        <v>128165962</v>
       </c>
       <c r="B19" t="n">
-        <v>91431</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730083</v>
+        <v>729916</v>
       </c>
       <c r="R19" t="n">
-        <v>7121514</v>
+        <v>7121715</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2435,7 +2436,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165956</v>
+        <v>128165930</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,34 +2663,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729958</v>
+        <v>730154</v>
       </c>
       <c r="R22" t="n">
-        <v>7121839</v>
+        <v>7121446</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2723,6 +2727,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2749,7 +2758,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128165930</v>
+        <v>128165931</v>
       </c>
       <c r="B23" t="n">
         <v>57689</v>
@@ -2778,20 +2787,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730154</v>
+        <v>730017</v>
       </c>
       <c r="R23" t="n">
-        <v>7121446</v>
+        <v>7121813</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2828,7 +2833,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på samma tall</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2855,10 +2860,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165931</v>
+        <v>128165956</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2866,21 +2871,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2890,10 +2895,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730017</v>
+        <v>729958</v>
       </c>
       <c r="R24" t="n">
-        <v>7121813</v>
+        <v>7121839</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2926,11 +2931,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2960,7 +2960,7 @@
         <v>128165974</v>
       </c>
       <c r="B25" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128165959</v>
+        <v>128165951</v>
       </c>
       <c r="B26" t="n">
         <v>79089</v>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729945</v>
+        <v>730024</v>
       </c>
       <c r="R26" t="n">
-        <v>7121797</v>
+        <v>7121785</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128165951</v>
+        <v>128165959</v>
       </c>
       <c r="B27" t="n">
         <v>79089</v>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730024</v>
+        <v>729945</v>
       </c>
       <c r="R27" t="n">
-        <v>7121785</v>
+        <v>7121797</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128165926</v>
+        <v>128165969</v>
       </c>
       <c r="B28" t="n">
-        <v>91466</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3259,34 +3259,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730131</v>
+        <v>730111</v>
       </c>
       <c r="R28" t="n">
-        <v>7121481</v>
+        <v>7121506</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3327,6 +3330,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3345,10 +3349,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128165969</v>
+        <v>128165926</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>91466</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3356,37 +3360,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730111</v>
+        <v>730131</v>
       </c>
       <c r="R29" t="n">
-        <v>7121506</v>
+        <v>7121481</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3427,7 +3428,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128165948</v>
+        <v>128165957</v>
       </c>
       <c r="B34" t="n">
         <v>79089</v>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730039</v>
+        <v>729953</v>
       </c>
       <c r="R34" t="n">
-        <v>7121748</v>
+        <v>7121824</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3950,7 +3950,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128165957</v>
+        <v>128165948</v>
       </c>
       <c r="B35" t="n">
         <v>79089</v>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729953</v>
+        <v>730039</v>
       </c>
       <c r="R35" t="n">
-        <v>7121824</v>
+        <v>7121748</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4745,7 +4745,7 @@
         <v>128165939</v>
       </c>
       <c r="B43" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5238,10 +5238,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128221495</v>
+        <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5249,21 +5249,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730262</v>
+        <v>730239</v>
       </c>
       <c r="R48" t="n">
-        <v>7121551</v>
+        <v>7121592</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5309,6 +5309,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5335,10 +5340,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128221503</v>
+        <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5346,21 +5351,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5370,10 +5375,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730239</v>
+        <v>730262</v>
       </c>
       <c r="R49" t="n">
-        <v>7121592</v>
+        <v>7121551</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5406,11 +5411,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5437,32 +5437,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128221481</v>
+        <v>128221484</v>
       </c>
       <c r="B50" t="n">
-        <v>91431</v>
+        <v>91466</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730240</v>
+        <v>730055</v>
       </c>
       <c r="R50" t="n">
-        <v>7121639</v>
+        <v>7121821</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5534,32 +5534,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128221484</v>
+        <v>128221481</v>
       </c>
       <c r="B51" t="n">
-        <v>91466</v>
+        <v>91431</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730055</v>
+        <v>730240</v>
       </c>
       <c r="R51" t="n">
-        <v>7121821</v>
+        <v>7121639</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5631,56 +5631,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>98588</v>
+        <v>91431</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R52" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5718,67 +5710,74 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B53" t="n">
-        <v>91431</v>
+        <v>98591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R53" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5816,18 +5815,19 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6032,56 +6032,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128165941</v>
+        <v>128221489</v>
       </c>
       <c r="B56" t="n">
-        <v>98588</v>
+        <v>57686</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729946</v>
+        <v>730051</v>
       </c>
       <c r="R56" t="n">
-        <v>7121788</v>
+        <v>7121646</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6119,67 +6111,74 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128221489</v>
+        <v>128165941</v>
       </c>
       <c r="B57" t="n">
-        <v>57686</v>
+        <v>98591</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730051</v>
+        <v>729946</v>
       </c>
       <c r="R57" t="n">
-        <v>7121646</v>
+        <v>7121788</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6217,18 +6216,19 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128221494</v>
+        <v>128221485</v>
       </c>
       <c r="B60" t="n">
-        <v>80194</v>
+        <v>91466</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,34 +6444,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730250</v>
+        <v>730021</v>
       </c>
       <c r="R60" t="n">
-        <v>7121538</v>
+        <v>7121603</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6512,6 +6515,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6530,10 +6534,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128221485</v>
+        <v>128221494</v>
       </c>
       <c r="B61" t="n">
-        <v>91466</v>
+        <v>80194</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6541,37 +6545,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730021</v>
+        <v>730250</v>
       </c>
       <c r="R61" t="n">
-        <v>7121603</v>
+        <v>7121538</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6612,7 +6613,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6631,32 +6631,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128221498</v>
+        <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>98588</v>
+        <v>91484</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730083</v>
+        <v>730247</v>
       </c>
       <c r="R62" t="n">
-        <v>7121587</v>
+        <v>7121509</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6728,32 +6728,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128221502</v>
+        <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91484</v>
+        <v>91431</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730247</v>
+        <v>730261</v>
       </c>
       <c r="R63" t="n">
-        <v>7121509</v>
+        <v>7121621</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6825,32 +6825,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128221480</v>
+        <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>91431</v>
+        <v>98591</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>730261</v>
+        <v>730083</v>
       </c>
       <c r="R64" t="n">
-        <v>7121621</v>
+        <v>7121587</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165930</v>
+        <v>128165956</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,38 +2663,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730154</v>
+        <v>729958</v>
       </c>
       <c r="R22" t="n">
-        <v>7121446</v>
+        <v>7121839</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2727,11 +2723,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2758,7 +2749,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128165931</v>
+        <v>128165930</v>
       </c>
       <c r="B23" t="n">
         <v>57689</v>
@@ -2787,16 +2778,20 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730017</v>
+        <v>730154</v>
       </c>
       <c r="R23" t="n">
-        <v>7121813</v>
+        <v>7121446</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2833,7 +2828,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2860,10 +2855,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165956</v>
+        <v>128165931</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2871,21 +2866,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2895,10 +2890,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729958</v>
+        <v>730017</v>
       </c>
       <c r="R24" t="n">
-        <v>7121839</v>
+        <v>7121813</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2931,6 +2926,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3248,10 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128165969</v>
+        <v>128165926</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>91466</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3259,37 +3259,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730111</v>
+        <v>730131</v>
       </c>
       <c r="R28" t="n">
-        <v>7121506</v>
+        <v>7121481</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3330,7 +3327,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3349,10 +3345,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128165926</v>
+        <v>128165969</v>
       </c>
       <c r="B29" t="n">
-        <v>91466</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3360,34 +3356,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730131</v>
+        <v>730111</v>
       </c>
       <c r="R29" t="n">
-        <v>7121481</v>
+        <v>7121506</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3428,6 +3427,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128165927</v>
+        <v>128165958</v>
       </c>
       <c r="B39" t="n">
-        <v>91466</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4361,21 +4361,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730137</v>
+        <v>729942</v>
       </c>
       <c r="R39" t="n">
-        <v>7121478</v>
+        <v>7121803</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128165942</v>
+        <v>128165965</v>
       </c>
       <c r="B40" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4458,34 +4458,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730136</v>
+        <v>730086</v>
       </c>
       <c r="R40" t="n">
-        <v>7121772</v>
+        <v>7121516</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4526,6 +4529,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4544,10 +4548,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128165958</v>
+        <v>128165927</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>91466</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4555,21 +4559,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4579,10 +4583,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729942</v>
+        <v>730137</v>
       </c>
       <c r="R41" t="n">
-        <v>7121803</v>
+        <v>7121478</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4641,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128165965</v>
+        <v>128165942</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>91484</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4652,37 +4656,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730086</v>
+        <v>730136</v>
       </c>
       <c r="R42" t="n">
-        <v>7121516</v>
+        <v>7121772</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4723,7 +4724,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165938</v>
+        <v>128165963</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729946</v>
+        <v>730066</v>
       </c>
       <c r="R2" t="n">
-        <v>7121687</v>
+        <v>7121525</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165919</v>
+        <v>128165947</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729911</v>
+        <v>730042</v>
       </c>
       <c r="R3" t="n">
-        <v>7121731</v>
+        <v>7121730</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -847,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165963</v>
+        <v>128165938</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730066</v>
+        <v>729946</v>
       </c>
       <c r="R4" t="n">
-        <v>7121525</v>
+        <v>7121687</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -957,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -975,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128165947</v>
+        <v>128165919</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730042</v>
+        <v>729911</v>
       </c>
       <c r="R5" t="n">
-        <v>7121730</v>
+        <v>7121731</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1046,6 +1041,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1762,7 +1762,7 @@
         <v>128165925</v>
       </c>
       <c r="B13" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128165943</v>
       </c>
       <c r="B14" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>128165944</v>
       </c>
       <c r="B15" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,48 +2062,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128165922</v>
+        <v>128165946</v>
       </c>
       <c r="B16" t="n">
-        <v>91431</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730083</v>
+        <v>730160</v>
       </c>
       <c r="R16" t="n">
-        <v>7121514</v>
+        <v>7121748</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2144,7 +2141,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,7 +2159,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165946</v>
+        <v>128165961</v>
       </c>
       <c r="B17" t="n">
         <v>79089</v>
@@ -2198,10 +2194,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730160</v>
+        <v>729905</v>
       </c>
       <c r="R17" t="n">
-        <v>7121748</v>
+        <v>7121772</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2260,7 +2256,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128165961</v>
+        <v>128165962</v>
       </c>
       <c r="B18" t="n">
         <v>79089</v>
@@ -2295,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729905</v>
+        <v>729916</v>
       </c>
       <c r="R18" t="n">
-        <v>7121772</v>
+        <v>7121715</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2357,32 +2353,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128165962</v>
+        <v>128165935</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>97463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2392,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>729916</v>
+        <v>730109</v>
       </c>
       <c r="R19" t="n">
-        <v>7121715</v>
+        <v>7121506</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2454,10 +2450,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128165935</v>
+        <v>128165922</v>
       </c>
       <c r="B20" t="n">
-        <v>97462</v>
+        <v>91432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,34 +2461,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730109</v>
+        <v>730083</v>
       </c>
       <c r="R20" t="n">
-        <v>7121506</v>
+        <v>7121514</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2533,6 +2532,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>128165974</v>
       </c>
       <c r="B25" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128165951</v>
+        <v>128165959</v>
       </c>
       <c r="B26" t="n">
         <v>79089</v>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730024</v>
+        <v>729945</v>
       </c>
       <c r="R26" t="n">
-        <v>7121785</v>
+        <v>7121797</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128165959</v>
+        <v>128165951</v>
       </c>
       <c r="B27" t="n">
         <v>79089</v>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729945</v>
+        <v>730024</v>
       </c>
       <c r="R27" t="n">
-        <v>7121797</v>
+        <v>7121785</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3251,7 +3251,7 @@
         <v>128165926</v>
       </c>
       <c r="B28" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128165955</v>
+        <v>128165933</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3457,34 +3457,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>729973</v>
+        <v>730045</v>
       </c>
       <c r="R30" t="n">
-        <v>7121813</v>
+        <v>7121802</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3517,6 +3521,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3543,7 +3552,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128165933</v>
+        <v>128165932</v>
       </c>
       <c r="B31" t="n">
         <v>57689</v>
@@ -3572,20 +3581,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730045</v>
+        <v>730083</v>
       </c>
       <c r="R31" t="n">
-        <v>7121802</v>
+        <v>7121500</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3649,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128165932</v>
+        <v>128165955</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,21 +3665,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3684,10 +3689,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730083</v>
+        <v>729973</v>
       </c>
       <c r="R32" t="n">
-        <v>7121500</v>
+        <v>7121813</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3720,11 +3725,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4551,7 +4551,7 @@
         <v>128165927</v>
       </c>
       <c r="B41" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>128165942</v>
       </c>
       <c r="B42" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>128165939</v>
       </c>
       <c r="B43" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5238,10 +5238,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128221503</v>
+        <v>128221495</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5249,21 +5249,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730239</v>
+        <v>730262</v>
       </c>
       <c r="R48" t="n">
-        <v>7121592</v>
+        <v>7121551</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5309,11 +5309,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5340,10 +5335,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128221495</v>
+        <v>128221503</v>
       </c>
       <c r="B49" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5351,21 +5346,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5375,10 +5370,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730262</v>
+        <v>730239</v>
       </c>
       <c r="R49" t="n">
-        <v>7121551</v>
+        <v>7121592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5411,6 +5406,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5440,7 +5440,7 @@
         <v>128221484</v>
       </c>
       <c r="B50" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221481</v>
       </c>
       <c r="B51" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5631,48 +5631,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B52" t="n">
-        <v>91431</v>
+        <v>98592</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R52" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5710,74 +5718,67 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B53" t="n">
-        <v>98591</v>
+        <v>91432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R53" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5815,29 +5816,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128221482</v>
+        <v>128221487</v>
       </c>
       <c r="B54" t="n">
-        <v>91431</v>
+        <v>80223</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,37 +5845,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730021</v>
+        <v>730102</v>
       </c>
       <c r="R54" t="n">
-        <v>7121603</v>
+        <v>7121795</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5916,7 +5913,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5935,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128221487</v>
+        <v>128221482</v>
       </c>
       <c r="B55" t="n">
-        <v>80223</v>
+        <v>91432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5946,34 +5942,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730102</v>
+        <v>730021</v>
       </c>
       <c r="R55" t="n">
-        <v>7121795</v>
+        <v>7121603</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6014,6 +6013,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6032,48 +6032,56 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128221489</v>
+        <v>128165941</v>
       </c>
       <c r="B56" t="n">
-        <v>57686</v>
+        <v>98592</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730051</v>
+        <v>729946</v>
       </c>
       <c r="R56" t="n">
-        <v>7121646</v>
+        <v>7121788</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6111,74 +6119,67 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128165941</v>
+        <v>128221489</v>
       </c>
       <c r="B57" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729946</v>
+        <v>730051</v>
       </c>
       <c r="R57" t="n">
-        <v>7121788</v>
+        <v>7121646</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6216,67 +6217,63 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221486</v>
+        <v>128221500</v>
       </c>
       <c r="B58" t="n">
-        <v>91466</v>
+        <v>98592</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730186</v>
+        <v>730091</v>
       </c>
       <c r="R58" t="n">
-        <v>7121516</v>
+        <v>7121561</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6317,7 +6314,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6336,45 +6332,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221500</v>
+        <v>128221486</v>
       </c>
       <c r="B59" t="n">
-        <v>98591</v>
+        <v>91467</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730091</v>
+        <v>730186</v>
       </c>
       <c r="R59" t="n">
-        <v>7121561</v>
+        <v>7121516</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6415,6 +6414,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>128221485</v>
       </c>
       <c r="B60" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -1759,10 +1759,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128165925</v>
+        <v>128165943</v>
       </c>
       <c r="B13" t="n">
-        <v>91467</v>
+        <v>91485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730049</v>
+        <v>730059</v>
       </c>
       <c r="R13" t="n">
-        <v>7121812</v>
+        <v>7121540</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128165943</v>
+        <v>128165925</v>
       </c>
       <c r="B14" t="n">
-        <v>91485</v>
+        <v>91467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730059</v>
+        <v>730049</v>
       </c>
       <c r="R14" t="n">
-        <v>7121540</v>
+        <v>7121812</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128165935</v>
+        <v>128165922</v>
       </c>
       <c r="B19" t="n">
-        <v>97463</v>
+        <v>91432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,34 +2364,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730109</v>
+        <v>730083</v>
       </c>
       <c r="R19" t="n">
-        <v>7121506</v>
+        <v>7121514</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2432,6 +2435,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2450,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128165922</v>
+        <v>128165935</v>
       </c>
       <c r="B20" t="n">
-        <v>91432</v>
+        <v>97463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2461,37 +2465,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730083</v>
+        <v>730109</v>
       </c>
       <c r="R20" t="n">
-        <v>7121514</v>
+        <v>7121506</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2532,7 +2533,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -5238,10 +5238,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128221495</v>
+        <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5249,21 +5249,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730262</v>
+        <v>730239</v>
       </c>
       <c r="R48" t="n">
-        <v>7121551</v>
+        <v>7121592</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5309,6 +5309,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5335,10 +5340,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128221503</v>
+        <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5346,21 +5351,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5370,10 +5375,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730239</v>
+        <v>730262</v>
       </c>
       <c r="R49" t="n">
-        <v>7121592</v>
+        <v>7121551</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5406,11 +5411,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5631,56 +5631,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128165940</v>
+        <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>98592</v>
+        <v>91432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729939</v>
+        <v>730169</v>
       </c>
       <c r="R52" t="n">
-        <v>7121786</v>
+        <v>7121486</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5718,67 +5710,74 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128221483</v>
+        <v>128165940</v>
       </c>
       <c r="B53" t="n">
-        <v>91432</v>
+        <v>98592</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730169</v>
+        <v>729939</v>
       </c>
       <c r="R53" t="n">
-        <v>7121486</v>
+        <v>7121786</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5816,18 +5815,19 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6235,45 +6235,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221500</v>
+        <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>98592</v>
+        <v>91467</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730091</v>
+        <v>730186</v>
       </c>
       <c r="R58" t="n">
-        <v>7121561</v>
+        <v>7121516</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6314,6 +6317,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6332,48 +6336,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221486</v>
+        <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>91467</v>
+        <v>98592</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730186</v>
+        <v>730091</v>
       </c>
       <c r="R59" t="n">
-        <v>7121516</v>
+        <v>7121561</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6414,7 +6415,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>128221493</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221484</v>
       </c>
       <c r="B50" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221481</v>
       </c>
       <c r="B51" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>128165940</v>
       </c>
       <c r="B53" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221487</v>
       </c>
       <c r="B54" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>128221482</v>
       </c>
       <c r="B55" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6032,56 +6032,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128165941</v>
+        <v>128221489</v>
       </c>
       <c r="B56" t="n">
-        <v>98592</v>
+        <v>57713</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729946</v>
+        <v>730051</v>
       </c>
       <c r="R56" t="n">
-        <v>7121788</v>
+        <v>7121646</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6119,67 +6111,74 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128221489</v>
+        <v>128165941</v>
       </c>
       <c r="B57" t="n">
-        <v>57686</v>
+        <v>98619</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730051</v>
+        <v>729946</v>
       </c>
       <c r="R57" t="n">
-        <v>7121646</v>
+        <v>7121788</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6217,18 +6216,19 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128221485</v>
       </c>
       <c r="B60" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128221494</v>
       </c>
       <c r="B61" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -5437,32 +5437,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128221484</v>
+        <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91494</v>
+        <v>91459</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730055</v>
+        <v>730240</v>
       </c>
       <c r="R50" t="n">
-        <v>7121821</v>
+        <v>7121639</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5534,32 +5534,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128221481</v>
+        <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91459</v>
+        <v>91494</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730240</v>
+        <v>730055</v>
       </c>
       <c r="R51" t="n">
-        <v>7121639</v>
+        <v>7121821</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128221487</v>
+        <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>80250</v>
+        <v>91459</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,34 +5845,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730102</v>
+        <v>730021</v>
       </c>
       <c r="R54" t="n">
-        <v>7121795</v>
+        <v>7121603</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5913,6 +5916,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5931,10 +5935,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128221482</v>
+        <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>91459</v>
+        <v>80250</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,37 +5946,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730021</v>
+        <v>730102</v>
       </c>
       <c r="R55" t="n">
-        <v>7121603</v>
+        <v>7121795</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6013,7 +6014,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6032,48 +6032,56 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128221489</v>
+        <v>128165941</v>
       </c>
       <c r="B56" t="n">
-        <v>57713</v>
+        <v>98619</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730051</v>
+        <v>729946</v>
       </c>
       <c r="R56" t="n">
-        <v>7121646</v>
+        <v>7121788</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6111,74 +6119,67 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128165941</v>
+        <v>128221489</v>
       </c>
       <c r="B57" t="n">
-        <v>98619</v>
+        <v>57713</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729946</v>
+        <v>730051</v>
       </c>
       <c r="R57" t="n">
-        <v>7121788</v>
+        <v>7121646</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6216,19 +6217,18 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128221485</v>
+        <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>91494</v>
+        <v>80221</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,37 +6444,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730021</v>
+        <v>730250</v>
       </c>
       <c r="R60" t="n">
-        <v>7121603</v>
+        <v>7121538</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6515,7 +6512,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6534,10 +6530,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128221494</v>
+        <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>80221</v>
+        <v>91494</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6545,34 +6541,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730250</v>
+        <v>730021</v>
       </c>
       <c r="R61" t="n">
-        <v>7121538</v>
+        <v>7121603</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6613,6 +6612,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91790</v>
+        <v>91800</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91494</v>
+        <v>91504</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91494</v>
+        <v>91504</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91494</v>
+        <v>91504</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96865</v>
+        <v>96878</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>128221493</v>
       </c>
       <c r="B45" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>128221489</v>
       </c>
       <c r="B57" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>128221493</v>
       </c>
       <c r="B45" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>128221489</v>
       </c>
       <c r="B57" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>128221493</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>128221489</v>
       </c>
       <c r="B57" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>128221493</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>128221489</v>
       </c>
       <c r="B57" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6651,14 +6651,10 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6828,7 +6824,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6925,7 +6921,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7022,7 +7018,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>128221503</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128221495</v>
       </c>
       <c r="B49" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>128221487</v>
       </c>
       <c r="B55" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128221494</v>
       </c>
       <c r="B60" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
         <v>128221492</v>
       </c>
       <c r="B44" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128221497</v>
       </c>
       <c r="B46" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128221496</v>
       </c>
       <c r="B47" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5440,7 +5440,7 @@
         <v>128221481</v>
       </c>
       <c r="B50" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128221484</v>
       </c>
       <c r="B51" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>128221483</v>
       </c>
       <c r="B52" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128221482</v>
       </c>
       <c r="B54" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128221486</v>
       </c>
       <c r="B58" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>128221500</v>
       </c>
       <c r="B59" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6533,7 +6533,7 @@
         <v>128221485</v>
       </c>
       <c r="B61" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128221502</v>
       </c>
       <c r="B62" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6727,7 +6727,7 @@
         <v>128221480</v>
       </c>
       <c r="B63" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>128221498</v>
       </c>
       <c r="B64" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -6921,7 +6921,7 @@
         <v>128221479</v>
       </c>
       <c r="B65" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>128221499</v>
       </c>
       <c r="B66" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128165963</v>
+        <v>128221479</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730066</v>
+        <v>730141</v>
       </c>
       <c r="R2" t="n">
-        <v>7121525</v>
+        <v>7121775</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165947</v>
+        <v>128221492</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730042</v>
+        <v>730055</v>
       </c>
       <c r="R3" t="n">
-        <v>7121730</v>
+        <v>7121821</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128165938</v>
+        <v>128165925</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729946</v>
+        <v>730049</v>
       </c>
       <c r="R4" t="n">
-        <v>7121687</v>
+        <v>7121812</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128165919</v>
+        <v>128165926</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729911</v>
+        <v>730131</v>
       </c>
       <c r="R5" t="n">
-        <v>7121731</v>
+        <v>7121481</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1041,11 +1041,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128165953</v>
+        <v>128165927</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730005</v>
+        <v>730137</v>
       </c>
       <c r="R6" t="n">
-        <v>7121826</v>
+        <v>7121478</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1169,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128165945</v>
+        <v>128221484</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,13 +1199,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730227</v>
+        <v>730055</v>
       </c>
       <c r="R7" t="n">
-        <v>7121677</v>
+        <v>7121821</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,22 +1249,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128165949</v>
+        <v>128221485</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,37 +1272,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730055</v>
+        <v>730021</v>
       </c>
       <c r="R8" t="n">
-        <v>7121817</v>
+        <v>7121603</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1345,13 +1343,14 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1363,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128165970</v>
+        <v>128221486</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1401,13 +1400,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730103</v>
+        <v>730186</v>
       </c>
       <c r="R9" t="n">
-        <v>7121499</v>
+        <v>7121516</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,7 +1451,7 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1464,45 +1463,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128165950</v>
+        <v>128165922</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730039</v>
+        <v>730083</v>
       </c>
       <c r="R10" t="n">
-        <v>7121797</v>
+        <v>7121514</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1543,6 +1545,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1561,51 +1564,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128165972</v>
+        <v>128221480</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730154</v>
+        <v>730261</v>
       </c>
       <c r="R11" t="n">
-        <v>7121458</v>
+        <v>7121621</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1643,51 +1643,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128165954</v>
+        <v>128221481</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1697,13 +1696,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729978</v>
+        <v>730240</v>
       </c>
       <c r="R12" t="n">
-        <v>7121810</v>
+        <v>7121639</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1747,44 +1746,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128165943</v>
+        <v>128221482</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,13 +1796,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730059</v>
+        <v>730021</v>
       </c>
       <c r="R13" t="n">
-        <v>7121540</v>
+        <v>7121603</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1848,63 +1847,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128165925</v>
+        <v>128221483</v>
       </c>
       <c r="B14" t="n">
-        <v>91467</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730049</v>
+        <v>730169</v>
       </c>
       <c r="R14" t="n">
-        <v>7121812</v>
+        <v>7121486</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1942,67 +1938,63 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128165944</v>
+        <v>128165945</v>
       </c>
       <c r="B15" t="n">
-        <v>91485</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730125</v>
+        <v>730227</v>
       </c>
       <c r="R15" t="n">
-        <v>7121462</v>
+        <v>7121677</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2043,7 +2035,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2065,11 +2056,11 @@
         <v>128165946</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2159,14 +2150,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128165961</v>
+        <v>128165947</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2194,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729905</v>
+        <v>730042</v>
       </c>
       <c r="R17" t="n">
-        <v>7121772</v>
+        <v>7121730</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2256,14 +2247,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128165962</v>
+        <v>128165948</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2291,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729916</v>
+        <v>730039</v>
       </c>
       <c r="R18" t="n">
-        <v>7121715</v>
+        <v>7121748</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2353,48 +2344,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128165922</v>
+        <v>128165949</v>
       </c>
       <c r="B19" t="n">
-        <v>91432</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730083</v>
+        <v>730055</v>
       </c>
       <c r="R19" t="n">
-        <v>7121514</v>
+        <v>7121817</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2435,7 +2423,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2454,32 +2441,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128165935</v>
+        <v>128165950</v>
       </c>
       <c r="B20" t="n">
-        <v>97463</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730109</v>
+        <v>730039</v>
       </c>
       <c r="R20" t="n">
-        <v>7121506</v>
+        <v>7121797</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2551,14 +2538,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128165960</v>
+        <v>128165951</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2580,19 +2567,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>729928</v>
+        <v>730024</v>
       </c>
       <c r="R21" t="n">
-        <v>7121753</v>
+        <v>7121785</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2633,7 +2617,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2652,14 +2635,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128165956</v>
+        <v>128165953</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2687,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729958</v>
+        <v>730005</v>
       </c>
       <c r="R22" t="n">
-        <v>7121839</v>
+        <v>7121826</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2749,49 +2732,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128165930</v>
+        <v>128165954</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730154</v>
+        <v>729978</v>
       </c>
       <c r="R23" t="n">
-        <v>7121446</v>
+        <v>7121810</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2824,11 +2803,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2855,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128165931</v>
+        <v>128165955</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2890,7 +2864,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730017</v>
+        <v>729973</v>
       </c>
       <c r="R24" t="n">
         <v>7121813</v>
@@ -2926,11 +2900,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2957,32 +2926,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128165974</v>
+        <v>128165956</v>
       </c>
       <c r="B25" t="n">
-        <v>98509</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2992,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729928</v>
+        <v>729958</v>
       </c>
       <c r="R25" t="n">
-        <v>7121682</v>
+        <v>7121839</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3054,14 +3023,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128165959</v>
+        <v>128165957</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3089,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729945</v>
+        <v>729953</v>
       </c>
       <c r="R26" t="n">
-        <v>7121797</v>
+        <v>7121824</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3151,14 +3120,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128165951</v>
+        <v>128165958</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3186,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730024</v>
+        <v>729942</v>
       </c>
       <c r="R27" t="n">
-        <v>7121785</v>
+        <v>7121803</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3248,32 +3217,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128165926</v>
+        <v>128165959</v>
       </c>
       <c r="B28" t="n">
-        <v>91467</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3283,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730131</v>
+        <v>729945</v>
       </c>
       <c r="R28" t="n">
-        <v>7121481</v>
+        <v>7121797</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3345,14 +3314,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128165969</v>
+        <v>128165960</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3383,10 +3352,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730111</v>
+        <v>729928</v>
       </c>
       <c r="R29" t="n">
-        <v>7121506</v>
+        <v>7121753</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3446,49 +3415,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128165933</v>
+        <v>128165961</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730045</v>
+        <v>729905</v>
       </c>
       <c r="R30" t="n">
-        <v>7121802</v>
+        <v>7121772</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3521,11 +3486,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3552,32 +3512,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128165932</v>
+        <v>128165962</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3587,10 +3547,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730083</v>
+        <v>729916</v>
       </c>
       <c r="R31" t="n">
-        <v>7121500</v>
+        <v>7121715</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3623,11 +3583,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3654,14 +3609,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128165955</v>
+        <v>128165963</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3689,10 +3644,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>729973</v>
+        <v>730066</v>
       </c>
       <c r="R32" t="n">
-        <v>7121813</v>
+        <v>7121525</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3751,45 +3706,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128165934</v>
+        <v>128165965</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730051</v>
+        <v>730086</v>
       </c>
       <c r="R33" t="n">
-        <v>7121815</v>
+        <v>7121516</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3824,17 +3782,13 @@
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3853,14 +3807,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128165957</v>
+        <v>128165967</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3882,16 +3836,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>729953</v>
+        <v>730095</v>
       </c>
       <c r="R34" t="n">
-        <v>7121824</v>
+        <v>7121521</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3932,6 +3889,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3950,14 +3908,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128165948</v>
+        <v>128165969</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3979,16 +3937,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730039</v>
+        <v>730111</v>
       </c>
       <c r="R35" t="n">
-        <v>7121748</v>
+        <v>7121506</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4029,6 +3990,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4047,14 +4009,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128165967</v>
+        <v>128165970</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4085,10 +4047,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730095</v>
+        <v>730103</v>
       </c>
       <c r="R36" t="n">
-        <v>7121521</v>
+        <v>7121499</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4151,11 +4113,11 @@
         <v>128165971</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4249,32 +4211,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128165928</v>
+        <v>128165972</v>
       </c>
       <c r="B38" t="n">
-        <v>80223</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4287,10 +4249,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>729932</v>
+        <v>730154</v>
       </c>
       <c r="R38" t="n">
-        <v>7121695</v>
+        <v>7121458</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4350,14 +4312,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128165958</v>
+        <v>128165973</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4385,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729942</v>
+        <v>730204</v>
       </c>
       <c r="R39" t="n">
-        <v>7121803</v>
+        <v>7121456</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4447,14 +4409,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128165965</v>
+        <v>128221503</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4476,22 +4438,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730086</v>
+        <v>730239</v>
       </c>
       <c r="R40" t="n">
-        <v>7121516</v>
+        <v>7121592</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4523,20 +4482,24 @@
           <t>2025-09-01</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -4548,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128165927</v>
+        <v>128165938</v>
       </c>
       <c r="B41" t="n">
-        <v>91467</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4559,34 +4522,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730137</v>
+        <v>729946</v>
       </c>
       <c r="R41" t="n">
-        <v>7121478</v>
+        <v>7121687</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4627,6 +4593,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4645,10 +4612,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128165942</v>
+        <v>128221494</v>
       </c>
       <c r="B42" t="n">
-        <v>91485</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4656,21 +4623,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4680,13 +4647,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730136</v>
+        <v>730250</v>
       </c>
       <c r="R42" t="n">
-        <v>7121772</v>
+        <v>7121538</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4730,7 +4697,7 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -4742,52 +4709,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128165939</v>
+        <v>128221495</v>
       </c>
       <c r="B43" t="n">
-        <v>98592</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729923</v>
+        <v>730262</v>
       </c>
       <c r="R43" t="n">
-        <v>7121820</v>
+        <v>7121551</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4825,14 +4788,13 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -4844,48 +4806,51 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128221492</v>
+        <v>128165928</v>
       </c>
       <c r="B44" t="n">
-        <v>91848</v>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730055</v>
+        <v>729932</v>
       </c>
       <c r="R44" t="n">
-        <v>7121821</v>
+        <v>7121695</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4923,50 +4888,51 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128221493</v>
+        <v>128221487</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4976,10 +4942,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730032</v>
+        <v>730102</v>
       </c>
       <c r="R45" t="n">
-        <v>7121700</v>
+        <v>7121795</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5014,11 +4980,6 @@
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5036,39 +4997,39 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128221497</v>
+        <v>128221489</v>
       </c>
       <c r="B46" t="n">
-        <v>98724</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5078,10 +5039,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730112</v>
+        <v>730051</v>
       </c>
       <c r="R46" t="n">
-        <v>7121785</v>
+        <v>7121646</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5133,39 +5094,39 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128221496</v>
+        <v>128165919</v>
       </c>
       <c r="B47" t="n">
-        <v>98724</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5175,13 +5136,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730168</v>
+        <v>729911</v>
       </c>
       <c r="R47" t="n">
-        <v>7121738</v>
+        <v>7121731</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5213,35 +5174,39 @@
           <t>2025-09-01</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128221503</v>
+        <v>128165930</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5249,37 +5214,41 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730239</v>
+        <v>730154</v>
       </c>
       <c r="R48" t="n">
-        <v>7121592</v>
+        <v>7121446</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5313,7 +5282,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Både äldre och färska ringhack på samma tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5328,7 +5297,7 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -5340,10 +5309,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128221495</v>
+        <v>128165931</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5351,21 +5320,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5375,13 +5344,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730262</v>
+        <v>730017</v>
       </c>
       <c r="R49" t="n">
-        <v>7121551</v>
+        <v>7121813</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5411,6 +5380,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5425,44 +5399,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128221481</v>
+        <v>128165932</v>
       </c>
       <c r="B50" t="n">
-        <v>91514</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5472,13 +5446,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730240</v>
+        <v>730083</v>
       </c>
       <c r="R50" t="n">
-        <v>7121639</v>
+        <v>7121500</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5508,6 +5482,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5522,22 +5501,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128221484</v>
+        <v>128165933</v>
       </c>
       <c r="B51" t="n">
-        <v>91550</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5545,37 +5524,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730055</v>
+        <v>730045</v>
       </c>
       <c r="R51" t="n">
-        <v>7121821</v>
+        <v>7121802</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5605,6 +5588,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5619,44 +5607,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128221483</v>
+        <v>128165934</v>
       </c>
       <c r="B52" t="n">
-        <v>91514</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5666,13 +5654,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730169</v>
+        <v>730051</v>
       </c>
       <c r="R52" t="n">
-        <v>7121486</v>
+        <v>7121815</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5702,6 +5690,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5716,68 +5709,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128165940</v>
+        <v>128221493</v>
       </c>
       <c r="B53" t="n">
-        <v>98619</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729939</v>
+        <v>730032</v>
       </c>
       <c r="R53" t="n">
-        <v>7121786</v>
+        <v>7121700</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5809,20 +5794,24 @@
           <t>2025-09-01</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -5834,10 +5823,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128221482</v>
+        <v>128165974</v>
       </c>
       <c r="B54" t="n">
-        <v>91514</v>
+        <v>99035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,40 +5834,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730021</v>
+        <v>729928</v>
       </c>
       <c r="R54" t="n">
-        <v>7121603</v>
+        <v>7121682</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5916,67 +5902,70 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128221487</v>
+        <v>128165939</v>
       </c>
       <c r="B55" t="n">
-        <v>80178</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730102</v>
+        <v>729923</v>
       </c>
       <c r="R55" t="n">
-        <v>7121795</v>
+        <v>7121820</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6014,28 +6003,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128165941</v>
+        <v>128165940</v>
       </c>
       <c r="B56" t="n">
-        <v>98619</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6062,7 +6052,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -6075,10 +6065,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729946</v>
+        <v>729939</v>
       </c>
       <c r="R56" t="n">
-        <v>7121788</v>
+        <v>7121786</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6138,48 +6128,56 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128221489</v>
+        <v>128165941</v>
       </c>
       <c r="B57" t="n">
-        <v>57724</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730051</v>
+        <v>729946</v>
       </c>
       <c r="R57" t="n">
-        <v>7121646</v>
+        <v>7121788</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6217,66 +6215,64 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128221486</v>
+        <v>128221496</v>
       </c>
       <c r="B58" t="n">
-        <v>91550</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730186</v>
+        <v>730168</v>
       </c>
       <c r="R58" t="n">
-        <v>7121516</v>
+        <v>7121738</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6329,17 +6325,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128221500</v>
+        <v>128221497</v>
       </c>
       <c r="B59" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6371,10 +6367,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730091</v>
+        <v>730112</v>
       </c>
       <c r="R59" t="n">
-        <v>7121561</v>
+        <v>7121785</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6433,32 +6429,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128221494</v>
+        <v>128221498</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6468,10 +6464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730250</v>
+        <v>730083</v>
       </c>
       <c r="R60" t="n">
-        <v>7121538</v>
+        <v>7121587</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6523,55 +6519,52 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128221485</v>
+        <v>128221499</v>
       </c>
       <c r="B61" t="n">
-        <v>91550</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730021</v>
+        <v>730110</v>
       </c>
       <c r="R61" t="n">
-        <v>7121603</v>
+        <v>7121785</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6612,7 +6605,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6624,37 +6616,41 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128221502</v>
+        <v>128221500</v>
       </c>
       <c r="B62" t="n">
-        <v>91570</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6662,10 +6658,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730247</v>
+        <v>730091</v>
       </c>
       <c r="R62" t="n">
-        <v>7121509</v>
+        <v>7121561</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6724,10 +6720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128221480</v>
+        <v>128165935</v>
       </c>
       <c r="B63" t="n">
-        <v>91514</v>
+        <v>97983</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6735,21 +6731,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6759,13 +6755,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730261</v>
+        <v>730109</v>
       </c>
       <c r="R63" t="n">
-        <v>7121621</v>
+        <v>7121506</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6809,306 +6805,15 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>128221498</v>
-      </c>
-      <c r="B64" t="n">
-        <v>98724</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Svartbacken, Vb</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>730083</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7121587</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>128221479</v>
-      </c>
-      <c r="B65" t="n">
-        <v>96970</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>53</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Svartbacken, Vb</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>730141</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7121775</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>128221499</v>
-      </c>
-      <c r="B66" t="n">
-        <v>98724</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Svartbacken, Vb</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>730110</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7121785</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24414-2024 artfynd.xlsx
+++ b/artfynd/A 24414-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221479</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221492</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165925</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165926</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165927</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221484</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221485</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221486</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165922</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221482</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221483</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165946</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165947</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165948</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165949</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165950</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165951</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165953</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165954</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165955</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165956</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165957</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,6 +3038,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165958</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165959</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3121,6 +3246,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165960</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3218,6 +3348,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165961</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3315,6 +3450,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165962</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3412,6 +3552,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165963</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3513,6 +3658,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165965</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3614,6 +3764,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165967</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3715,6 +3870,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165969</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3816,6 +3976,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165970</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3917,6 +4082,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165971</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4018,6 +4188,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165972</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4115,6 +4290,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165973</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4216,6 +4396,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165938</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4317,6 +4502,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165928</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4414,6 +4604,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221487</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4511,6 +4706,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221489</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4613,6 +4813,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165919</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4719,6 +4924,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165930</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4821,6 +5031,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165931</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4923,6 +5138,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165932</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5029,6 +5249,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165933</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5131,6 +5356,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165934</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5233,6 +5463,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221493</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5330,6 +5565,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165974</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5432,6 +5672,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165939</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5538,6 +5783,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165940</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5644,6 +5894,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165941</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5742,6 +5997,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221496</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5839,6 +6099,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221497</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5936,6 +6201,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221498</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6033,6 +6303,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221499</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6130,6 +6405,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221500</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6227,6 +6507,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165935</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6324,6 +6609,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221480</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6421,6 +6711,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221481</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6518,6 +6813,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165945</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6620,6 +6920,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221503</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6717,6 +7022,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221494</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6814,8 +7124,77 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221495</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>